--- a/naver-place-crawler/results_nail/동구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/동구_네일샵.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>yeji4438@naver.com</t>
+          <t>a_nail@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6777,13 +6777,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q68" t="n">
         <v>1219</v>
       </c>
       <c r="R68" t="n">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>
@@ -7525,13 +7525,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q76" t="n">
         <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/동구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/동구_네일샵.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>유리네일</t>
+          <t>라예샵</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sfsf0525@naver.com</t>
+          <t>mh124510@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1353-8292</t>
+          <t>0507-1329-0164</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 38 1층 101호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 16 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uri_nail_</t>
+          <t>https://blog.naver.com/mh124510</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
-        <v>94</v>
+        <v>186</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1234163292</t>
+          <t>1698965767</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234163292</t>
+          <t>https://m.place.naver.com/place/1698965767</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뾰로롱네일</t>
+          <t>반디인하우스 도화앨리웨이점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mjy22977@naver.com</t>
+          <t>bandinhouse_dohwa@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1302-6657</t>
+          <t>0507-1392-8241</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
+          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>81</v>
+        <v>341</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="R3" t="n">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2058778627</t>
+          <t>1485881474</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058778627</t>
+          <t>https://m.place.naver.com/place/1485881474</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>구이일이샵</t>
+          <t>오드리뷰티</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rtreat_way@naver.com</t>
+          <t>saerom66@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1343-9212</t>
+          <t>0507-1367-2646</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 면개포로 15 1층 1호</t>
+          <t>인천광역시 미추홀구 주안로 102 오드리뷰티 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://instagram.com/9212_nail</t>
+          <t>https://www.instagram.com/audreybeauty._1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="R4" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1957115704</t>
+          <t>1722511887</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1957115704</t>
+          <t>https://m.place.naver.com/place/1722511887</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,25 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>젤리네일</t>
+          <t>피부&amp;네일 미나뷰티샵</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mi2013@naver.com</t>
+          <t>jsm90300@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1407-9030</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
+          <t>인천광역시 서구 가정로 246 2층 미나뷰티샵</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1SGa70g</t>
+          <t>https://youtu.be/z9XWwEdP1oM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -884,13 +888,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pjws</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -899,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>390</v>
+        <v>232</v>
       </c>
       <c r="Q5" t="n">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="R5" t="n">
-        <v>497</v>
+        <v>293</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1140244485</t>
+          <t>1837576332</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140244485</t>
+          <t>https://m.place.naver.com/place/1837576332</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -936,29 +944,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>린다뷰티</t>
+          <t>네일오숑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>linda2017v@naver.com</t>
+          <t>dong_fcpae@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1422-6954</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로35번길 21-3 1층</t>
+          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lindabeauty.2017/</t>
+          <t>https://www.instagram.com/nail_osyong/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="Q6" t="n">
-        <v>246</v>
+        <v>19</v>
       </c>
       <c r="R6" t="n">
-        <v>325</v>
+        <v>279</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1636516132</t>
+          <t>1518702391</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636516132</t>
+          <t>https://m.place.naver.com/place/1518702391</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>반하리뷰티</t>
+          <t>두아네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>runningfam@naver.com</t>
+          <t>zolongky@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1312-2207</t>
+          <t>0507-1367-8198</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 91 3층 반하리뷰티</t>
+          <t>인천광역시 미추홀구 능해길 12 용현대우아파트 상가동 201호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/banhari0311</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1062,7 +1066,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1083,17 +1087,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="Q7" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1478084350</t>
+          <t>1806218865</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478084350</t>
+          <t>https://m.place.naver.com/place/1806218865</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일 연출</t>
+          <t>네일스프링</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>052young@naver.com</t>
+          <t>wldus318@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1390-8318</t>
+          <t>0507-1465-2797</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로162번길 22-2 1층</t>
+          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/directing.n</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,7 +1160,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1181,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1751393842</t>
+          <t>2098983836</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1751393842</t>
+          <t>https://m.place.naver.com/place/2098983836</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>오오샵 가좌점</t>
+          <t>뷰티더한_네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dodofamily_mam@naver.com</t>
+          <t>fom05@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1409-2216</t>
+          <t>0507-1328-7134</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
+          <t>인천광역시 서구 건지로 264 1층 108호 일부</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,7 +1254,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1260,10 +1264,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ujgg</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>396</v>
+        <v>235</v>
       </c>
       <c r="Q9" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>436</v>
+        <v>239</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1153356301</t>
+          <t>1338980593</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153356301</t>
+          <t>https://m.place.naver.com/place/1338980593</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1312,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>도화네일</t>
+          <t>네일고운</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gsqnls2u@naver.com</t>
+          <t>promemoria11@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1373-9131</t>
+          <t>0507-1301-1928</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
+          <t>인천광역시 미추홀구 주안로 86 주안역 지하도 상가 109호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dohwa_nail_</t>
+          <t>https://www.instagram.com/nail_goeun</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1369,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>691</v>
+        <v>38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>693</v>
+        <v>41</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1155887763</t>
+          <t>1691519525</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155887763</t>
+          <t>https://m.place.naver.com/place/1691519525</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1406,25 +1414,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>수네일아트</t>
+          <t>왕비네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>very_cake@naver.com</t>
+          <t>sulai@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1443-1136</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로90번길 6 4층402호 수네일아트</t>
+          <t>인천광역시 미추홀구 수봉안길13번길 2 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://instagram.com/leh4377</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1434,7 +1446,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1459,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1690186584</t>
+          <t>2055499585</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1690186584</t>
+          <t>https://m.place.naver.com/place/2055499585</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1508,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>루즈뷰티</t>
+          <t>the네일샵</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dbtl0705@naver.com</t>
+          <t>raphaell1004@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1430-6778</t>
+          <t>0507-1341-2360</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 75 102호</t>
+          <t>인천광역시 동구 화도진로 84 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/meixiang65956777?igsh=ZWlpbml2dXhieGRu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1528,7 +1540,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1549,17 +1561,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1580,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2040581322</t>
+          <t>1183303268</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040581322</t>
+          <t>https://m.place.naver.com/place/1183303268</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1590,39 +1602,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
+          <t>네일아이</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dritn-nail_a_o@naver.com</t>
+          <t>army1300@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1325-1015</t>
+          <t>0507-1324-8849</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 장천로 57 1층</t>
+          <t>인천광역시 중구 개항로 19-1 1층 네일아이</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://m.themosttimes.co.kr/39655</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1632,10 +1644,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sdev</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1647,13 +1663,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="Q13" t="n">
-        <v>117</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1678,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1166150967</t>
+          <t>1827399146</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166150967</t>
+          <t>https://m.place.naver.com/place/1827399146</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1700,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>제로네일</t>
+          <t>뷰티송</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>seeat_f@naver.com</t>
+          <t>beautysong7@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1359-4583</t>
+          <t>0507-1399-1155</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
+          <t>인천광역시 동구 송림로 25 인송상가 106호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zeronail_art</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1716,7 +1732,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1726,13 +1742,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46f8b</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1741,13 +1761,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>331</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1776,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1613054835</t>
+          <t>1018868110</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1613054835</t>
+          <t>https://m.place.naver.com/place/1018868110</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1778,29 +1798,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>피부&amp;네일 미나뷰티샵</t>
+          <t>네일 날씨 : 맑음.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dksdidwhdk@naver.com</t>
+          <t>malgeum_nail@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1407-9030</t>
+          <t>0507-1338-9518</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 246 2층 미나뷰티샵</t>
+          <t>인천광역시 중구 우현로 67 신포지하도상가 37호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://youtu.be/z9XWwEdP1oM</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1810,7 +1830,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1826,7 +1846,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1835,13 +1855,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>232</v>
+        <v>107</v>
       </c>
       <c r="Q15" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="R15" t="n">
-        <v>293</v>
+        <v>119</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1870,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1837576332</t>
+          <t>1170688757</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1837576332</t>
+          <t>https://m.place.naver.com/place/1170688757</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1872,25 +1892,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>송림동네일</t>
+          <t>이지네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>yeps0406@naver.com</t>
+          <t>easynailgainmiga@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1481-8813</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 123 104호</t>
+          <t>인천광역시 서구 열우물로282번길 25 103호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/song_rim_dong_nail</t>
+          <t>https://www.instagram.com/easy.nlash</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1925,13 +1949,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1940,17 +1964,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1132799210</t>
+          <t>2055850137</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1132799210</t>
+          <t>https://m.place.naver.com/place/2055850137</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1962,29 +1986,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>미추홀구 레벨업 네일뷰티 도화점</t>
+          <t>구이일이샵</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>draw-grow@naver.com</t>
+          <t>uomdf77@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1440-6558</t>
+          <t>0507-1343-9212</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 135 해피타운 103호</t>
+          <t>인천광역시 서구 면개포로 15 1층 1호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/levelup_nailstudio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1994,7 +2018,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2019,13 +2043,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>843</v>
+        <v>84</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>846</v>
+        <v>85</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2058,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1204613930</t>
+          <t>1957115704</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1204613930</t>
+          <t>https://m.place.naver.com/place/1957115704</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2056,29 +2080,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일팔레트</t>
+          <t>용쥬르샵 인천본점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nail4season@naver.com</t>
+          <t>iiidydwn@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1334-0294</t>
+          <t>032-423-2963</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
+          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palette_nailll</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2088,7 +2112,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2098,10 +2122,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc039a</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>X</t>
@@ -2113,13 +2141,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>302</v>
+        <v>662</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="R18" t="n">
-        <v>308</v>
+        <v>717</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2156,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1167629339</t>
+          <t>1845960167</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167629339</t>
+          <t>https://m.place.naver.com/place/1845960167</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2150,29 +2178,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>에스네일</t>
+          <t>슈링네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>snail4324@naver.com</t>
+          <t>tjddk6025@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1406-3132</t>
+          <t>0507-1355-4556</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
+          <t>인천광역시 미추홀구 주안로 86 주안역지하상가 198호슈링네일</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snail0070</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2182,7 +2210,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2192,10 +2220,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vjxb</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>X</t>
@@ -2203,17 +2235,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="Q19" t="n">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="R19" t="n">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2254,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>38286683</t>
+          <t>1276113416</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38286683</t>
+          <t>https://m.place.naver.com/place/1276113416</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2244,34 +2276,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>리마인드뷰티</t>
+          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bacsubac@naver.com</t>
+          <t>dritn-nail_a_o@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1312-5095</t>
+          <t>0507-1325-1015</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 109 2층 온다s뷰티</t>
+          <t>인천광역시 미추홀구 장천로 57 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re_mind_beauty</t>
+          <t>https://m.themosttimes.co.kr/39655</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2286,10 +2318,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43muq</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>X</t>
@@ -2301,13 +2337,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>117</v>
       </c>
       <c r="R20" t="n">
-        <v>38</v>
+        <v>204</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2352,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1978227491</t>
+          <t>1166150967</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1978227491</t>
+          <t>https://m.place.naver.com/place/1166150967</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2338,29 +2374,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일,포슬</t>
+          <t>아르떼네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kirari__@naver.com</t>
+          <t>arte__nail_@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1386-5035</t>
+          <t>0507-1323-0926</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
+          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_poseul_</t>
+          <t>https://blog.naver.com/arte__nail_</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2375,7 +2411,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2386,7 +2422,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2395,13 +2431,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="Q21" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="R21" t="n">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,17 +2446,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1050625355</t>
+          <t>1775601804</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050625355</t>
+          <t>https://m.place.naver.com/place/1775601804</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2432,29 +2468,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>슈링네일</t>
+          <t>백설공주네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>tjddk6025@naver.com</t>
+          <t>k3249093@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1355-4556</t>
+          <t>0507-1422-5107</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86 주안역지하상가 198호슈링네일</t>
+          <t>인천광역시 동구 송현로 18</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/snow_white.nail</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2464,7 +2500,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2485,17 +2521,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="Q22" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="R22" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2540,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1276113416</t>
+          <t>1579326733</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1276113416</t>
+          <t>https://m.place.naver.com/place/1579326733</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2526,39 +2562,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>뷰티송</t>
+          <t>디두네일 D.do nail studio</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>beautysong7@naver.com</t>
+          <t>ddonail12@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1399-1155</t>
+          <t>0507-1423-8033</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 25 인송상가 106호</t>
+          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnIYDxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2568,10 +2604,14 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wm70qab</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>O</t>
@@ -2583,13 +2623,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R23" t="n">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2638,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1018868110</t>
+          <t>2003325308</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1018868110</t>
+          <t>https://m.place.naver.com/place/2003325308</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2620,39 +2660,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>마이린 네일</t>
+          <t>인블리네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>myrin_nail@naver.com</t>
+          <t>bbobbolee2@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1364-9606</t>
+          <t>070-7643-2243</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kqfkxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2662,10 +2702,14 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v1lk</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>O</t>
@@ -2677,13 +2721,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>199</v>
+        <v>416</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>1221</v>
       </c>
       <c r="R24" t="n">
-        <v>203</v>
+        <v>1637</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2736,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1373786401</t>
+          <t>63265483</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1373786401</t>
+          <t>https://m.place.naver.com/place/63265483</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2714,29 +2758,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>미미네일</t>
+          <t>아비엥또네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kensgirl1206@naver.com</t>
+          <t>cc3214@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1378-8871</t>
+          <t>0507-1340-6448</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 85 2층 미미네일</t>
+          <t>인천광역시 미추홀구 석정로351번길 13 1층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/mimi.nail_beauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2746,7 +2790,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2762,7 +2806,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2771,13 +2815,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>55</v>
+        <v>428</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>70</v>
+        <v>430</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2830,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1738480958</t>
+          <t>1754281841</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1738480958</t>
+          <t>https://m.place.naver.com/place/1754281841</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2808,12 +2852,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>룩앳미네일</t>
+          <t>송림동네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>lmy1042@naver.com</t>
+          <t>mhsong0103kk@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2821,7 +2865,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 94</t>
+          <t>인천광역시 동구 샛골로 123 104호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2857,17 +2901,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,17 +2920,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>722059236</t>
+          <t>1132799210</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/722059236</t>
+          <t>https://m.place.naver.com/place/1132799210</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2898,29 +2942,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>언니쓰네일샵</t>
+          <t>봉숭아네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>qgd2557@naver.com</t>
+          <t>a_nail@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0507-1333-2250</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 서구 옻우물로8번길 10 1층 103호 언니쓰네일샵</t>
+          <t>인천광역시 동구 송미로 17-4 송림패션몰e동105호 스텔라헤어메이크. 내</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uniss_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2930,7 +2970,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2951,17 +2991,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,17 +3010,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1983714719</t>
+          <t>1910022457</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1983714719</t>
+          <t>https://m.place.naver.com/place/1910022457</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2992,29 +3032,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일무드</t>
+          <t>미다움네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_m_1106@naver.com</t>
+          <t>luna_pic@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1311-6940</t>
+          <t>0507-1442-0506</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 9 1층 네일무드</t>
+          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_mood22</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3024,7 +3064,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3049,13 +3089,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>206</v>
+        <v>22</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="R28" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,17 +3104,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1544163213</t>
+          <t>1835371224</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1544163213</t>
+          <t>https://m.place.naver.com/place/1835371224</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3086,39 +3126,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>이루아네일</t>
+          <t>올라운더네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>woo_vely_@naver.com</t>
+          <t>allroundernail@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1400-0973</t>
+          <t>0507-1359-5371</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
+          <t>인천광역시 미추홀구 주안로 116 1층 103 A호 올라운더네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000070812</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3128,10 +3168,14 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5iwa5</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>X</t>
@@ -3143,13 +3187,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3158,17 +3202,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2089020201</t>
+          <t>1165613309</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089020201</t>
+          <t>https://m.place.naver.com/place/1165613309</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3180,29 +3224,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>단홍뷰티</t>
+          <t>유리네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>danhong44@naver.com</t>
+          <t>sfsf0525@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1322-9298</t>
+          <t>0507-1353-8292</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 중구 신포로 32 1층 (본비반트 헤어)</t>
+          <t>인천광역시 동구 송현로 38 1층 101호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/uri_nail_</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3212,7 +3256,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3233,17 +3277,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="Q30" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="R30" t="n">
-        <v>349</v>
+        <v>94</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3252,17 +3296,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1111139597</t>
+          <t>1234163292</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1111139597</t>
+          <t>https://m.place.naver.com/place/1234163292</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3274,25 +3318,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>고운손</t>
+          <t>네일체인지</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ipbunsign@naver.com</t>
+          <t>j2lang@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1350-8716</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
+          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 상가 B1층 1032호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3302,7 +3350,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3312,10 +3360,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4d3wc</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3327,13 +3379,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>159</v>
+        <v>313</v>
       </c>
       <c r="Q31" t="n">
         <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>161</v>
+        <v>315</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3342,17 +3394,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1926481487</t>
+          <t>1330641272</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926481487</t>
+          <t>https://m.place.naver.com/place/1330641272</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3364,25 +3416,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>네일바이슈</t>
+          <t>반하리뷰티</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7571khs@naver.com</t>
+          <t>moonvely147@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1312-2207</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로35번길 21-2 네일바이슈</t>
+          <t>인천광역시 미추홀구 주안로 91 3층 반하리뷰티</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailby_sue</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3392,7 +3448,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3402,10 +3458,14 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4x9eu</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>X</t>
@@ -3417,13 +3477,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="Q32" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="R32" t="n">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,17 +3492,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1304540142</t>
+          <t>1478084350</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1304540142</t>
+          <t>https://m.place.naver.com/place/1478084350</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3454,29 +3514,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1124네일&amp;래쉬</t>
+          <t>미미네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>yeps0406@naver.com</t>
+          <t>kensgirl1206@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1363-6780</t>
+          <t>0507-1378-8871</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 동구 인중로680번길 9 1124네일&amp;래쉬</t>
+          <t>인천광역시 중구 우현로 85 2층 미미네일</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1124_nail_lash</t>
+          <t>http://www.instagram.com/mimi.nail_beauty</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3511,13 +3571,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>214</v>
+        <v>55</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R33" t="n">
-        <v>230</v>
+        <v>70</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,17 +3586,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1126025095</t>
+          <t>1738480958</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1126025095</t>
+          <t>https://m.place.naver.com/place/1738480958</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3548,34 +3608,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>문제성 손,발 오감네일 도화점</t>
+          <t>이루아네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ogam_foot_nail@naver.com</t>
+          <t>nec1153@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1388-5117</t>
+          <t>0507-1400-0973</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
+          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ogam_foot_nail</t>
+          <t>https://zero.gongbiz.kr/shop/S000070812</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3585,7 +3645,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3605,13 +3665,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>660</v>
+        <v>136</v>
       </c>
       <c r="Q34" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="R34" t="n">
-        <v>726</v>
+        <v>159</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3620,17 +3680,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1716147754</t>
+          <t>2089020201</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716147754</t>
+          <t>https://m.place.naver.com/place/2089020201</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3642,29 +3702,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일맑음</t>
+          <t>제로네일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>s1514@naver.com</t>
+          <t>seeat_f@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1489-0530</t>
+          <t>0507-1359-4583</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
+          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuneungyeong4</t>
+          <t>https://www.instagram.com/zeronail_art</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3699,13 +3759,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>235</v>
+        <v>334</v>
       </c>
       <c r="Q35" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3714,17 +3774,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1539397163</t>
+          <t>1613054835</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539397163</t>
+          <t>https://m.place.naver.com/place/1613054835</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3736,29 +3796,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>라움뷰티 인천점</t>
+          <t>1124네일&amp;래쉬</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>raumnail89@naver.com</t>
+          <t>yeps0406@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1322-1397</t>
+          <t>0507-1363-6780</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 360 상가 1층 104호 라움</t>
+          <t>인천광역시 동구 인중로680번길 9 1124네일&amp;래쉬</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/___raum_nail</t>
+          <t>https://www.instagram.com/1124_nail_lash</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3784,7 +3844,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3793,13 +3853,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="Q36" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="R36" t="n">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3808,17 +3868,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1287439678</t>
+          <t>1126025095</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1287439678</t>
+          <t>https://m.place.naver.com/place/1126025095</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3890,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>뷰티더한_네일</t>
+          <t>수네일아트</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>fom05@naver.com</t>
+          <t>very_cake@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3843,12 +3903,12 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 서구 건지로 264 1층 108호 일부</t>
+          <t>인천광역시 미추홀구 주안로90번길 6 4층402호 수네일아트</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_adorable_heyrin?igsh=c3dqcThsM3Uzb3Uz</t>
+          <t>http://instagram.com/leh4377</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3883,13 +3943,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>235</v>
+        <v>59</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R37" t="n">
-        <v>239</v>
+        <v>66</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3898,17 +3958,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1338980593</t>
+          <t>1690186584</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338980593</t>
+          <t>https://m.place.naver.com/place/1690186584</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3920,25 +3980,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>봉숭아네일</t>
+          <t>언니쓰네일샵</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>a_nail@naver.com</t>
+          <t>qgd2557@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1333-2250</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송미로 17-4 송림패션몰e동105호 스텔라헤어메이크. 내</t>
+          <t>인천광역시 서구 옻우물로8번길 10 1층 103호 언니쓰네일샵</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/uniss_nail</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3948,7 +4012,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3969,17 +4033,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3988,17 +4052,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1910022457</t>
+          <t>1983714719</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910022457</t>
+          <t>https://m.place.naver.com/place/1983714719</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4010,29 +4074,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>루미랑네일</t>
+          <t>네일맑음</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jine_blog@naver.com</t>
+          <t>s1514@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1371-1706</t>
+          <t>0507-1489-0530</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rumirang_nail</t>
+          <t>https://www.instagram.com/yuneungyeong4</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4067,10 +4131,10 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="Q39" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="R39" t="n">
         <v>303</v>
@@ -4082,17 +4146,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1156304078</t>
+          <t>1539397163</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156304078</t>
+          <t>https://m.place.naver.com/place/1539397163</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4104,29 +4168,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>아르떼네일</t>
+          <t>룩앳미네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>arte__nail_@naver.com</t>
+          <t>lmy1042@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1323-0926</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
+          <t>인천광역시 동구 솔빛로 94</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/arte__nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4136,12 +4196,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4152,22 +4212,22 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>392</v>
+        <v>4</v>
       </c>
       <c r="Q40" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>451</v>
+        <v>5</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4176,17 +4236,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1775601804</t>
+          <t>722059236</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1775601804</t>
+          <t>https://m.place.naver.com/place/722059236</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4198,34 +4258,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>아젤리아네일</t>
+          <t>네일루아</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dlwlgus0914@naver.com</t>
+          <t>wldud0735@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1491-3901</t>
+          <t>0507-1439-8987</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 서구 장고개로287번길 6-2 1층 101호</t>
+          <t>인천광역시 미추홀구 숙골로87번길 14 107호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlwlgus0914</t>
+          <t>http://pf.kakao.com/_yxmDPxj</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4235,7 +4295,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4246,7 +4306,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4255,13 +4315,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>131</v>
+        <v>205</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>144</v>
+        <v>209</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4270,17 +4330,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1393226062</t>
+          <t>1678699503</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1393226062</t>
+          <t>https://m.place.naver.com/place/1678699503</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4292,34 +4352,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>디두네일 D.do nail studio</t>
+          <t>고운손</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ddonail12@naver.com</t>
+          <t>ghghrjftm@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0507-1423-8033</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
+          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Ukxhxmn</t>
+          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4340,7 +4396,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4349,13 +4405,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="Q42" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4364,17 +4420,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2003325308</t>
+          <t>1926481487</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003325308</t>
+          <t>https://m.place.naver.com/place/1926481487</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4386,29 +4442,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>퍼플</t>
+          <t>봉구네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>art-lavender@naver.com</t>
+          <t>94rnrdudal@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>070-8692-3990</t>
+          <t>0507-1320-0380</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 21</t>
+          <t>인천광역시 미추홀구 주안로 86</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bonggu_nail</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4418,7 +4474,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4439,17 +4495,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>133</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4458,17 +4514,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1182840289</t>
+          <t>1965492062</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1182840289</t>
+          <t>https://m.place.naver.com/place/1965492062</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4480,34 +4536,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>아비엥또네일</t>
+          <t>린다뷰티</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>cc3214@naver.com</t>
+          <t>linda2017v@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1340-6448</t>
+          <t>0507-1422-6954</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로351번길 13 1층</t>
+          <t>인천광역시 중구 우현로35번길 21-3 1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_HHusxj</t>
+          <t>https://www.instagram.com/lindabeauty.2017/</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4528,7 +4584,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4537,13 +4593,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>423</v>
+        <v>79</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>246</v>
       </c>
       <c r="R44" t="n">
-        <v>425</v>
+        <v>325</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4552,17 +4608,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1754281841</t>
+          <t>1636516132</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754281841</t>
+          <t>https://m.place.naver.com/place/1636516132</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4574,29 +4630,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>반디인하우스 도화앨리웨이점</t>
+          <t>젤리네일</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>bandinhouse_dohwa@naver.com</t>
+          <t>mi2013@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1392-8241</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
+          <t>https://open.kakao.com/o/s1SGa70g</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4622,7 +4674,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4631,13 +4683,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>340</v>
+        <v>391</v>
       </c>
       <c r="Q45" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="R45" t="n">
-        <v>419</v>
+        <v>498</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4646,17 +4698,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1485881474</t>
+          <t>1140244485</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485881474</t>
+          <t>https://m.place.naver.com/place/1140244485</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4668,29 +4720,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>백설공주네일</t>
+          <t>퍼플</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>k3249093@naver.com</t>
+          <t>art-lavender@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1422-5107</t>
+          <t>070-8692-3990</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 18</t>
+          <t>인천광역시 동구 솔빛로 21</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snow_white.nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4700,7 +4752,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4721,17 +4773,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,17 +4792,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1579326733</t>
+          <t>1182840289</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579326733</t>
+          <t>https://m.place.naver.com/place/1182840289</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4762,29 +4814,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>라예샵</t>
+          <t>미추홀구 레벨업 네일뷰티 도화점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>mh124510@naver.com</t>
+          <t>seeat_f@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1329-0164</t>
+          <t>0507-1440-6558</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 16 1층</t>
+          <t>인천광역시 미추홀구 경인로 135 해피타운 103호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mh124510</t>
+          <t>https://www.instagram.com/levelup_nailstudio</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4799,7 +4851,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4819,13 +4871,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>179</v>
+        <v>855</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>187</v>
+        <v>858</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4834,17 +4886,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1698965767</t>
+          <t>1204613930</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1698965767</t>
+          <t>https://m.place.naver.com/place/1204613930</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4856,34 +4908,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>네일루아</t>
+          <t>마벨네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>wldud0735@naver.com</t>
+          <t>yelee6080@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0507-1439-8987</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 14 107호</t>
+          <t>인천광역시 동구 수문통로 43 2층 202호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxmDPxj</t>
+          <t>https://www.instagram.com/ma._.belle_nail</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4904,7 +4952,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4913,14 +4961,14 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>202</v>
+        <v>3</v>
       </c>
       <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
         <v>4</v>
       </c>
-      <c r="R48" t="n">
-        <v>206</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>X</t>
@@ -4928,17 +4976,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1678699503</t>
+          <t>1535782131</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1678699503</t>
+          <t>https://m.place.naver.com/place/1535782131</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4950,29 +4998,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>왕비네일</t>
+          <t>잉큼잉큼네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sulai@naver.com</t>
+          <t>joli96@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1443-1136</t>
+          <t>032-772-2929</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 수봉안길13번길 2 1층</t>
+          <t>인천광역시 중구 자유공원로 26-1 잉큼잉큼네일</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/queennail1117</t>
+          <t>http://www.facebook.com/nail2929</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4987,7 +5035,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5007,13 +5055,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R49" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5022,17 +5070,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2055499585</t>
+          <t>37855121</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055499585</t>
+          <t>https://m.place.naver.com/place/37855121</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5044,29 +5092,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>the네일샵</t>
+          <t>라보떼 뷰티</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>raphaell1004@naver.com</t>
+          <t>dlatmfrl5824@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1341-2360</t>
+          <t>0507-1377-9030</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 84 1층</t>
+          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/labeaute7027__</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5076,7 +5124,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5097,17 +5145,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5116,17 +5164,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1183303268</t>
+          <t>1828605681</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1183303268</t>
+          <t>https://m.place.naver.com/place/1828605681</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5138,29 +5186,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일스프링</t>
+          <t>네일,포슬</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>witty_luna@naver.com</t>
+          <t>r__r_b@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1465-2797</t>
+          <t>0507-1386-5035</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
+          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___spring</t>
+          <t>https://www.instagram.com/nail_poseul_</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5195,13 +5243,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>117</v>
+        <v>408</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="R51" t="n">
-        <v>127</v>
+        <v>449</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5210,17 +5258,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2098983836</t>
+          <t>1050625355</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098983836</t>
+          <t>https://m.place.naver.com/place/1050625355</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5232,29 +5280,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일혜 도화점</t>
+          <t>주엘로</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nailhye_@naver.com</t>
+          <t>jew_ell@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1487-9095</t>
+          <t>0507-1431-9930</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
+          <t>인천광역시 미추홀구 숙골로112번길 2 2층 203호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.hye/</t>
+          <t>https://www.instagram.com/nail_jooello</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5289,13 +5337,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>316</v>
+        <v>229</v>
       </c>
       <c r="Q52" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R52" t="n">
-        <v>333</v>
+        <v>249</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5304,17 +5352,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1396481559</t>
+          <t>1125345899</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1396481559</t>
+          <t>https://m.place.naver.com/place/1125345899</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5326,29 +5374,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>루미네일 Lumi nail</t>
+          <t>도화네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>peanutshome02@naver.com</t>
+          <t>gsqnls2u@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1425-3210</t>
+          <t>0507-1373-9131</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 숭의역 4번출구 힐스테이트 상가 1층 메가커피 뒤쪽</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sBFtqrHh</t>
+          <t>https://www.instagram.com/dohwa_nail_</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5374,7 +5422,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5383,13 +5431,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>288</v>
+        <v>693</v>
       </c>
       <c r="Q53" t="n">
         <v>2</v>
       </c>
       <c r="R53" t="n">
-        <v>290</v>
+        <v>695</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5398,17 +5446,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>71612272</t>
+          <t>1155887763</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/71612272</t>
+          <t>https://m.place.naver.com/place/1155887763</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5420,34 +5468,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>꽃네일</t>
+          <t>네일 그리고, 봄</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>flower7868@naver.com</t>
+          <t>sj330035@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1338-6737</t>
+          <t>0507-1354-3366</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 69 중앙로지하도상가 28호</t>
+          <t>인천광역시 동구 화도진로34번길 5 네일 그리고, 봄 2층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flower_nail_24?igsh=OHVtM3NxaThjanMx</t>
+          <t>http://pf.kakao.com/_hxlLNb</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5468,7 +5516,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5477,13 +5525,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R54" t="n">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5492,17 +5540,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1456154411</t>
+          <t>1402084410</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456154411</t>
+          <t>https://m.place.naver.com/place/1402084410</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5514,25 +5562,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>마벨네일</t>
+          <t>네일미래쉬</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>tiia@naver.com</t>
+          <t>eungee77@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1389-2281</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 동구 수문통로 43 2층 202호</t>
+          <t>인천광역시 미추홀구 능해길 61-3 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ma._.belle_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5542,7 +5594,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5563,17 +5615,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q55" t="n">
         <v>3</v>
       </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
       <c r="R55" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5582,17 +5634,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1535782131</t>
+          <t>2002602411</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1535782131</t>
+          <t>https://m.place.naver.com/place/2002602411</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5604,29 +5656,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>이월네일</t>
+          <t>네일샤르망</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>feb1st-@naver.com</t>
+          <t>cea1222@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1403-9322</t>
+          <t>0507-1383-5061</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로733번길 27 제지층 101호</t>
+          <t>인천광역시 미추홀구 주안중로16번길 7 1층 그레이스타워 네일샤르망</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ewol.nail/</t>
+          <t>https://open.kakao.com/o/sW2y3z2g</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5661,13 +5713,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>6</v>
+        <v>121</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R56" t="n">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5676,17 +5728,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2028521125</t>
+          <t>1222205064</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028521125</t>
+          <t>https://m.place.naver.com/place/1222205064</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5698,34 +5750,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일 날씨 : 맑음.</t>
+          <t>넬덕</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>yolo__ej@naver.com</t>
+          <t>brushlounge@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1338-9518</t>
+          <t>0507-1469-2126</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 67 신포지하도상가 37호</t>
+          <t>인천광역시 미추홀구 석정로 405 더로프트2 1층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhpxedn</t>
+          <t>https://www.instagram.com/nelduck_87?igsh=NHRzanQ1Njd0c2Zy</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5746,7 +5798,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5755,13 +5807,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="Q57" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5770,17 +5822,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1170688757</t>
+          <t>2013586255</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1170688757</t>
+          <t>https://m.place.naver.com/place/2013586255</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5792,25 +5844,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>메이드빈</t>
+          <t>에스네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mizeme@naver.com</t>
+          <t>snail4324@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1406-3132</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로47번길 6 상가동 107호</t>
+          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/snail0070</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5820,7 +5876,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5841,17 +5897,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="R58" t="n">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5860,17 +5916,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1402327394</t>
+          <t>38286683</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1402327394</t>
+          <t>https://m.place.naver.com/place/38286683</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5882,29 +5938,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>미다움네일</t>
+          <t>미쓰리손톱</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>dksdidwhdk@naver.com</t>
+          <t>minsu900711@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1442-0506</t>
+          <t>0507-1365-1215</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
+          <t>인천광역시 동구 솔빛로 21 3층 305호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://instagram.com/me_daoom</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5914,7 +5970,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5935,17 +5991,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5954,17 +6010,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1835371224</t>
+          <t>1684702540</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835371224</t>
+          <t>https://m.place.naver.com/place/1684702540</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5976,34 +6032,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>로이네일</t>
+          <t>네일 연출</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>wlgus1647@naver.com</t>
+          <t>052young@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1350-5396</t>
+          <t>0507-1390-8318</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
+          <t>인천광역시 동구 샛골로162번길 22-2 1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vxkKMs/chat</t>
+          <t>https://www.instagram.com/directing.n</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6024,7 +6080,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6033,13 +6089,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>173</v>
+        <v>14</v>
       </c>
       <c r="Q60" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>190</v>
+        <v>16</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6048,17 +6104,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1765283529</t>
+          <t>1751393842</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765283529</t>
+          <t>https://m.place.naver.com/place/1751393842</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6070,25 +6126,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>디에즈네일</t>
+          <t>네일혜 도화점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>tombo613@naver.com</t>
+          <t>nailhye_@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1487-9095</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 52 104호 디에즈네일</t>
+          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://instagram.com/dieznail</t>
+          <t>https://www.instagram.com/_nail.hye/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6123,13 +6183,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="Q61" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="R61" t="n">
-        <v>250</v>
+        <v>342</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6138,17 +6198,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1520395186</t>
+          <t>1396481559</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520395186</t>
+          <t>https://m.place.naver.com/place/1396481559</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6160,34 +6220,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>오드리뷰티</t>
+          <t>루미랑네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>saerom66@naver.com</t>
+          <t>jine_blog@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1367-2646</t>
+          <t>0507-1371-1706</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 102 오드리뷰티 3층</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreybeauty._1</t>
+          <t>https://www.instagram.com/rumirang_nail</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6197,7 +6257,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6208,7 +6268,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6217,13 +6277,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>13</v>
+        <v>259</v>
       </c>
       <c r="Q62" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="R62" t="n">
-        <v>76</v>
+        <v>313</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6232,17 +6292,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1722511887</t>
+          <t>1156304078</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722511887</t>
+          <t>https://m.place.naver.com/place/1156304078</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6254,29 +6314,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일체인지</t>
+          <t>네일팔레트</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>j2lang@naver.com</t>
+          <t>nail4season@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1350-8716</t>
+          <t>0507-1334-0294</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 상가 B1층 1032호</t>
+          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.change</t>
+          <t>https://www.instagram.com/palette_nailll</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6311,13 +6371,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R63" t="n">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,17 +6386,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1330641272</t>
+          <t>1167629339</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330641272</t>
+          <t>https://m.place.naver.com/place/1167629339</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6348,30 +6408,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일오숑</t>
+          <t>로이네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>nailon22@naver.com</t>
+          <t>wlgus1647@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1350-5396</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
+          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_osyong/</t>
+          <t>http://pf.kakao.com/_vxkKMs/chat</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6392,7 +6456,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6401,13 +6465,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>258</v>
+        <v>172</v>
       </c>
       <c r="Q64" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R64" t="n">
-        <v>277</v>
+        <v>189</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6416,17 +6480,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1518702391</t>
+          <t>1765283529</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1518702391</t>
+          <t>https://m.place.naver.com/place/1765283529</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6438,39 +6502,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일 그리고, 봄</t>
+          <t>뾰로롱네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sj330035@naver.com</t>
+          <t>redberry5@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1354-3366</t>
+          <t>0507-1302-6657</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로34번길 5 네일 그리고, 봄 2층</t>
+          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_hxlLNb</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6486,22 +6550,22 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6510,17 +6574,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1402084410</t>
+          <t>2058778627</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1402084410</t>
+          <t>https://m.place.naver.com/place/2058778627</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6532,29 +6596,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>바비네일</t>
+          <t>리마인드뷰티</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>zasd43@naver.com</t>
+          <t>bacsubac@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1351-2629</t>
+          <t>0507-1312-5095</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 중구 개항로 44-1 1층 바비네일</t>
+          <t>인천광역시 동구 송림로 109 2층 온다s뷰티</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/re_mind_beauty</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6564,7 +6628,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6585,17 +6649,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="Q66" t="n">
         <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6604,17 +6668,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1166111581</t>
+          <t>1978227491</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166111581</t>
+          <t>https://m.place.naver.com/place/1978227491</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6626,29 +6690,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일샤르망</t>
+          <t>라움뷰티 인천점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>cea1222@naver.com</t>
+          <t>raumnail89@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1383-5061</t>
+          <t>0507-1322-1397</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로16번길 7 1층 그레이스타워 네일샤르망</t>
+          <t>인천광역시 미추홀구 석정로 360 상가 1층 104호 라움</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sW2y3z2g</t>
+          <t>https://www.instagram.com/___raum_nail</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6683,13 +6747,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>121</v>
+        <v>242</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="R67" t="n">
-        <v>125</v>
+        <v>286</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6698,17 +6762,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1222205064</t>
+          <t>1287439678</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222205064</t>
+          <t>https://m.place.naver.com/place/1287439678</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6720,34 +6784,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>인블리네일</t>
+          <t>디에즈네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>bbobbolee2@naver.com</t>
+          <t>judatv@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>070-7643-2243</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
+          <t>인천광역시 미추홀구 염전로202번길 52 104호 디에즈네일</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xhUIxmC</t>
+          <t>http://instagram.com/dieznail</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6768,7 +6828,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6777,13 +6837,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>410</v>
+        <v>225</v>
       </c>
       <c r="Q68" t="n">
-        <v>1219</v>
+        <v>25</v>
       </c>
       <c r="R68" t="n">
-        <v>1629</v>
+        <v>250</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6792,17 +6852,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>63265483</t>
+          <t>1520395186</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/63265483</t>
+          <t>https://m.place.naver.com/place/1520395186</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6814,29 +6874,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>봉구네일</t>
+          <t>루미네일 Lumi nail</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>94rnrdudal@naver.com</t>
+          <t>peanutshome02@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1320-0380</t>
+          <t>0507-1425-3210</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86</t>
+          <t>인천광역시 미추홀구 인주대로 5 숭의역 4번출구 힐스테이트 상가 1층 메가커피 뒤쪽</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bonggu_nail</t>
+          <t>https://open.kakao.com/o/sBFtqrHh</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6862,7 +6922,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6871,13 +6931,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>100</v>
+        <v>291</v>
       </c>
       <c r="Q69" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>131</v>
+        <v>293</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6886,17 +6946,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1965492062</t>
+          <t>71612272</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965492062</t>
+          <t>https://m.place.naver.com/place/71612272</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6908,12 +6968,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>라보떼 뷰티</t>
+          <t>네일바이슈</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>skgus7415@naver.com</t>
+          <t>7571khs@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -6921,12 +6981,12 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
+          <t>인천광역시 중구 우현로35번길 21-2 네일바이슈</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/labeaute7027__</t>
+          <t>https://www.instagram.com/nailby_sue</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6961,13 +7021,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="Q70" t="n">
-        <v>252</v>
+        <v>39</v>
       </c>
       <c r="R70" t="n">
-        <v>514</v>
+        <v>118</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6976,17 +7036,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1828605681</t>
+          <t>1304540142</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828605681</t>
+          <t>https://m.place.naver.com/place/1304540142</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6998,29 +7058,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>주엘로</t>
+          <t>바비네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jew_ell@naver.com</t>
+          <t>zasd43@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1431-9930</t>
+          <t>0507-1351-2629</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로112번길 2 2층 203호</t>
+          <t>인천광역시 중구 개항로 44-1 1층 바비네일</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_jooello</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7030,7 +7090,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7051,17 +7111,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>230</v>
+        <v>3</v>
       </c>
       <c r="Q71" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="R71" t="n">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7070,17 +7130,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1125345899</t>
+          <t>1166111581</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125345899</t>
+          <t>https://m.place.naver.com/place/1166111581</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7092,29 +7152,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>넬덕</t>
+          <t>무색</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>brushlounge@naver.com</t>
+          <t>415eunhasu@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1469-2126</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 405 더로프트2 1층</t>
+          <t>인천광역시 미추홀구 주안중로50번길 27-25 2층 204호 무색네일</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nelduck_87?igsh=NHRzanQ1Njd0c2Zy</t>
+          <t>https://www.instagram.com/_musaek</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7149,13 +7205,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="Q72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7164,17 +7220,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>2013586255</t>
+          <t>1875342279</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013586255</t>
+          <t>https://m.place.naver.com/place/1875342279</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7186,29 +7242,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>미쓰리손톱</t>
+          <t>아젤리아네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>minsu900711@naver.com</t>
+          <t>dlwlgus0914@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1365-1215</t>
+          <t>0507-1491-3901</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 21 3층 305호</t>
+          <t>인천광역시 서구 장고개로287번길 6-2 1층 101호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dlwlgus0914</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7218,12 +7274,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7239,17 +7295,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="Q73" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R73" t="n">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7258,17 +7314,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1684702540</t>
+          <t>1393226062</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1684702540</t>
+          <t>https://m.place.naver.com/place/1393226062</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7280,29 +7336,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>용쥬르샵 인천본점</t>
+          <t>문제성 손,발 오감네일 도화점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>iiidydwn@naver.com</t>
+          <t>ogam_foot_nail@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>032-423-2963</t>
+          <t>0507-1388-5117</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
+          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iiidydwn</t>
+          <t>https://blog.naver.com/ogam_foot_nail</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7337,13 +7393,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="Q74" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="R74" t="n">
-        <v>715</v>
+        <v>733</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7352,17 +7408,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1845960167</t>
+          <t>1716147754</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845960167</t>
+          <t>https://m.place.naver.com/place/1716147754</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7374,29 +7430,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>이지네일</t>
+          <t>오오샵 가좌점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>easynailgainmiga@naver.com</t>
+          <t>dodofamily_mam@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1481-8813</t>
+          <t>0507-1409-2216</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 열우물로282번길 25 103호</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/easy.nlash</t>
+          <t>https://www.instagram.com/55_allinone_shop</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7431,13 +7487,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>24</v>
+        <v>406</v>
       </c>
       <c r="Q75" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="R75" t="n">
-        <v>26</v>
+        <v>446</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7446,17 +7502,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2055850137</t>
+          <t>1153356301</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055850137</t>
+          <t>https://m.place.naver.com/place/1153356301</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7468,34 +7524,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일고운</t>
+          <t>마이린 네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>won_jieun@naver.com</t>
+          <t>myrin_nail@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1301-1928</t>
+          <t>0507-1364-9606</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86 주안역 지하도 상가 109호</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_goeun</t>
+          <t>http://pf.kakao.com/_kqfkxj</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7516,7 +7572,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7525,13 +7581,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>38</v>
+        <v>203</v>
       </c>
       <c r="Q76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>41</v>
+        <v>207</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7540,17 +7596,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1691519525</t>
+          <t>1373786401</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1691519525</t>
+          <t>https://m.place.naver.com/place/1373786401</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/동구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/동구_네일샵.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jsm90300@naver.com</t>
+          <t>auflaufl@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -888,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pjws</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -932,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1018,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1112,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1146,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail___spring</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,7 +1156,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q8" t="n">
         <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1210,7 +1206,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1225,11 +1221,7 @@
           <t>뷰티더한_네일</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>fom05@naver.com</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
@@ -1244,7 +1236,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_adorable_heyrin?igsh=c3dqcThsM3Uzb3Uz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,7 +1246,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1264,14 +1256,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ujgg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1308,7 +1296,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1390,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1424,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/queennail1117</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1446,7 +1434,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1496,7 +1484,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1511,11 +1499,7 @@
           <t>the네일샵</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>raphaell1004@naver.com</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
@@ -1590,7 +1574,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1608,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_naileye__judi?igsh=NnJic3Y2bnl0enVj&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1634,7 +1618,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1644,14 +1628,10 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4sdev</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1688,7 +1668,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1722,17 +1702,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xnIYDxj</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1742,14 +1722,10 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46f8b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>O</t>
@@ -1786,7 +1762,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1801,11 +1777,7 @@
           <t>네일 날씨 : 맑음.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>malgeum_nail@naver.com</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
@@ -1820,17 +1792,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xhpxedn</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1880,7 +1852,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1946,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1989,11 +1961,7 @@
           <t>구이일이샵</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>uomdf77@naver.com</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
@@ -2008,7 +1976,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/9212_nail</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2018,7 +1986,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2068,7 +2036,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2070,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/iiidydwn</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2112,24 +2080,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc039a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>X</t>
@@ -2166,7 +2130,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2181,11 +2145,7 @@
           <t>슈링네일</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>tjddk6025@naver.com</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
@@ -2220,14 +2180,10 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vjxb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>X</t>
@@ -2264,7 +2220,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2318,14 +2274,10 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43muq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>X</t>
@@ -2362,7 +2314,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2408,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2502,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2584,17 +2536,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_Ukxhxmn</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2604,14 +2556,10 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wm70qab</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>O</t>
@@ -2648,7 +2596,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2682,17 +2630,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xhUIxmC</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2702,14 +2650,10 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5v1lk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>O</t>
@@ -2746,7 +2690,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2780,17 +2724,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_HHusxj</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2840,7 +2784,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2814,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/song_rim_dong_nail</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2880,7 +2824,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2930,7 +2874,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2891,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>a_nail@naver.com</t>
+          <t>yeji4438@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -3020,7 +2964,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3035,11 +2979,7 @@
           <t>미다움네일</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>luna_pic@naver.com</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
@@ -3054,7 +2994,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/me_daoom</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3064,7 +3004,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3114,7 +3054,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3088,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/allroundernail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3158,24 +3098,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5iwa5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>X</t>
@@ -3212,7 +3148,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3242,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3276,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.change</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3350,7 +3286,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3360,14 +3296,10 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4d3wc</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3404,7 +3336,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3370,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/banhari0311</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3448,7 +3380,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3458,14 +3390,10 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4x9eu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>X</t>
@@ -3502,7 +3430,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3524,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3611,11 +3539,7 @@
           <t>이루아네일</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>nec1153@naver.com</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
@@ -3668,10 +3592,10 @@
         <v>136</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R34" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3690,7 +3614,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3708,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3853,13 +3777,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q36" t="n">
         <v>16</v>
       </c>
       <c r="R36" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3878,7 +3802,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3892,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4062,7 +3986,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4077,11 +4001,7 @@
           <t>네일맑음</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>s1514@naver.com</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
@@ -4156,7 +4076,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4166,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4260,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4355,11 +4275,7 @@
           <t>고운손</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ghghrjftm@naver.com</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -4405,13 +4321,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4430,7 +4346,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4440,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4534,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4624,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4718,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4817,11 +4733,7 @@
           <t>미추홀구 레벨업 네일뷰티 도화점</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>seeat_f@naver.com</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
@@ -4896,7 +4808,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4898,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5080,7 +4992,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5095,11 +5007,7 @@
           <t>라보떼 뷰티</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>dlatmfrl5824@naver.com</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
@@ -5174,7 +5082,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5176,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5270,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5377,11 +5285,7 @@
           <t>도화네일</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>gsqnls2u@naver.com</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
@@ -5456,7 +5360,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5454,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5619,13 +5523,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q55" t="n">
         <v>3</v>
       </c>
       <c r="R55" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5644,7 +5548,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5642,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5736,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5830,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6020,7 +5924,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6018,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6112,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6151,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6257,7 +6161,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6302,7 +6206,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6223,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>nail4season@naver.com</t>
+          <t>gkdisgmlwo@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -6371,13 +6275,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q63" t="n">
         <v>6</v>
       </c>
       <c r="R63" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6396,7 +6300,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6411,11 +6315,7 @@
           <t>로이네일</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>wlgus1647@naver.com</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
@@ -6490,7 +6390,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6484,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6599,11 +6499,7 @@
           <t>리마인드뷰티</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>bacsubac@naver.com</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
@@ -6678,7 +6574,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6668,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6758,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -6877,11 +6773,7 @@
           <t>루미네일 Lumi nail</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>peanutshome02@naver.com</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
@@ -6956,7 +6848,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7021,13 +6913,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q70" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R70" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7046,7 +6938,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7061,11 +6953,7 @@
           <t>바비네일</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>zasd43@naver.com</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
@@ -7140,7 +7028,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7118,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7212,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7306,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7400,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7494,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/동구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/동구_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>라예샵</t>
+          <t>1124네일&amp;래쉬</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mh124510@naver.com</t>
+          <t>yeps0406@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1329-0164</t>
+          <t>0507-1363-6780</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 16 1층</t>
+          <t>인천광역시 동구 인중로680번길 9 1124네일&amp;래쉬</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mh124510</t>
+          <t>https://www.instagram.com/1124_nail_lash</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>178</v>
+        <v>216</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>186</v>
+        <v>232</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1698965767</t>
+          <t>1126025095</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1698965767</t>
+          <t>https://m.place.naver.com/place/1126025095</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>반디인하우스 도화앨리웨이점</t>
+          <t>퍼플</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bandinhouse_dohwa@naver.com</t>
+          <t>art-lavender@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1392-8241</t>
+          <t>070-8692-3990</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
+          <t>인천광역시 동구 솔빛로 21</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>341</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>420</v>
+        <v>2</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1485881474</t>
+          <t>1182840289</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485881474</t>
+          <t>https://m.place.naver.com/place/1182840289</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>오드리뷰티</t>
+          <t>마이린 네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>saerom66@naver.com</t>
+          <t>myrin_nail@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1367-2646</t>
+          <t>0507-1364-9606</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 102 오드리뷰티 3층</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreybeauty._1</t>
+          <t>http://pf.kakao.com/_kqfkxj</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>13</v>
+        <v>203</v>
       </c>
       <c r="Q4" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1722511887</t>
+          <t>1373786401</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722511887</t>
+          <t>https://m.place.naver.com/place/1373786401</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피부&amp;네일 미나뷰티샵</t>
+          <t>제로네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>auflaufl@naver.com</t>
+          <t>seeat_f@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1407-9030</t>
+          <t>0507-1359-4583</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 246 2층 미나뷰티샵</t>
+          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://youtu.be/z9XWwEdP1oM</t>
+          <t>https://www.instagram.com/zeronail_art</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>232</v>
+        <v>335</v>
       </c>
       <c r="Q5" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>293</v>
+        <v>340</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1837576332</t>
+          <t>1613054835</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1837576332</t>
+          <t>https://m.place.naver.com/place/1613054835</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,25 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일오숑</t>
+          <t>봉구네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dong_fcpae@naver.com</t>
+          <t>94rnrdudal@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1320-0380</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
+          <t>인천광역시 미추홀구 주안로 86 지하상가 148/173호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_osyong/</t>
+          <t>https://www.instagram.com/bonggu_nail</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>260</v>
+        <v>102</v>
       </c>
       <c r="Q6" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="R6" t="n">
-        <v>279</v>
+        <v>132</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1518702391</t>
+          <t>1965492062</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1518702391</t>
+          <t>https://m.place.naver.com/place/1965492062</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>두아네일</t>
+          <t>고운손</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>zolongky@naver.com</t>
+          <t>ghghrjftm@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1367-8198</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 능해길 12 용현대우아파트 상가동 201호</t>
+          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>69</v>
+        <v>167</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1806218865</t>
+          <t>1926481487</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806218865</t>
+          <t>https://m.place.naver.com/place/1926481487</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1124,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일스프링</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>wldus318@naver.com</t>
-        </is>
-      </c>
+          <t>네일고운</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1465-2797</t>
+          <t>0507-1301-1928</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
+          <t>인천광역시 미추홀구 주안로 86 주안역 지하도 상가 109호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___spring</t>
+          <t>https://www.instagram.com/nail_goeun</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2098983836</t>
+          <t>1691519525</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098983836</t>
+          <t>https://m.place.naver.com/place/1691519525</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1218,25 +1214,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>뷰티더한_네일</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>미추홀구 레벨업 네일뷰티 도화점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>anh917759@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1328-7134</t>
+          <t>0507-1440-6558</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 건지로 264 1층 108호 일부</t>
+          <t>인천광역시 미추홀구 경인로 135 해피타운 103호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_adorable_heyrin?igsh=c3dqcThsM3Uzb3Uz</t>
+          <t>https://www.instagram.com/levelup_nailstudio</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>235</v>
+        <v>860</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>239</v>
+        <v>863</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1338980593</t>
+          <t>1204613930</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338980593</t>
+          <t>https://m.place.naver.com/place/1204613930</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일고운</t>
+          <t>왕비네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>promemoria11@naver.com</t>
+          <t>sulai@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1301-1928</t>
+          <t>0507-1443-1136</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86 주안역 지하도 상가 109호</t>
+          <t>인천광역시 미추홀구 수봉안길13번길 2 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_goeun</t>
+          <t>https://www.instagram.com/queennail1117</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1691519525</t>
+          <t>2055499585</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1691519525</t>
+          <t>https://m.place.naver.com/place/2055499585</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1402,29 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>왕비네일</t>
+          <t>이지네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sulai@naver.com</t>
+          <t>easynailgainmiga@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1443-1136</t>
+          <t>0507-1481-8813</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 수봉안길13번길 2 1층</t>
+          <t>인천광역시 서구 열우물로282번길 25 103호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/queennail1117</t>
+          <t>https://www.instagram.com/easy.nlash</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2055499585</t>
+          <t>2055850137</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055499585</t>
+          <t>https://m.place.naver.com/place/2055850137</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1496,25 +1496,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>the네일샵</t>
+          <t>에스네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1341-2360</t>
+          <t>0507-1406-3132</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 84 1층</t>
+          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/snail0070</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1183303268</t>
+          <t>38286683</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1183303268</t>
+          <t>https://m.place.naver.com/place/38286683</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1586,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일아이</t>
+          <t>루즈뷰티</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>army1300@naver.com</t>
+          <t>dbtl0705@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1324-8849</t>
+          <t>0507-1430-6778</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 중구 개항로 19-1 1층 네일아이</t>
+          <t>인천광역시 미추홀구 주안로 75 102호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_naileye__judi?igsh=NnJic3Y2bnl0enVj&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/meixiang65956777?igsh=ZWlpbml2dXhieGRu</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>193</v>
+        <v>47</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>199</v>
+        <v>48</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,17 +1658,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1827399146</t>
+          <t>2040581322</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1827399146</t>
+          <t>https://m.place.naver.com/place/2040581322</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1680,29 +1680,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>뷰티송</t>
+          <t>루미네일 Lumi nail</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>beautysong7@naver.com</t>
+          <t>peanutshome02@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1399-1155</t>
+          <t>0507-1425-3210</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 25 인송상가 106호</t>
+          <t>인천광역시 미추홀구 인주대로 5 숭의역 4번출구 힐스테이트 상가 1층 메가커피 뒤쪽</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnIYDxj</t>
+          <t>https://open.kakao.com/o/sBFtqrHh</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>292</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>24</v>
+        <v>294</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,17 +1752,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1018868110</t>
+          <t>71612272</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1018868110</t>
+          <t>https://m.place.naver.com/place/71612272</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1774,35 +1774,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일 날씨 : 맑음.</t>
+          <t>슈링네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1338-9518</t>
+          <t>0507-1355-4556</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 67 신포지하도상가 37호</t>
+          <t>인천광역시 미추홀구 주안로 86 주안역지하상가 198호슈링네일</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhpxedn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1818,22 +1818,22 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R15" t="n">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1842,17 +1842,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1170688757</t>
+          <t>1276113416</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1170688757</t>
+          <t>https://m.place.naver.com/place/1276113416</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1864,29 +1864,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>이지네일</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>easynailgainmiga@naver.com</t>
-        </is>
-      </c>
+          <t>네일,포슬</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1481-8813</t>
+          <t>0507-1386-5035</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 서구 열우물로282번길 25 103호</t>
+          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/easy.nlash</t>
+          <t>https://www.instagram.com/nail_poseul_</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1921,13 +1917,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>24</v>
+        <v>408</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="R16" t="n">
-        <v>26</v>
+        <v>449</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1936,17 +1932,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2055850137</t>
+          <t>1050625355</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055850137</t>
+          <t>https://m.place.naver.com/place/1050625355</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1958,25 +1954,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>구이일이샵</t>
+          <t>뾰로롱네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1343-9212</t>
+          <t>0507-1302-6657</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 면개포로 15 1층 1호</t>
+          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://instagram.com/9212_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1986,7 +1982,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2007,17 +2003,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2026,17 +2022,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1957115704</t>
+          <t>2058778627</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1957115704</t>
+          <t>https://m.place.naver.com/place/2058778627</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2048,29 +2044,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>용쥬르샵 인천본점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>iiidydwn@naver.com</t>
-        </is>
-      </c>
+          <t>루미랑네일</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>032-423-2963</t>
+          <t>0507-1371-1706</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iiidydwn</t>
+          <t>https://www.instagram.com/rumirang_nail</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2085,7 +2077,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2105,13 +2097,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>662</v>
+        <v>261</v>
       </c>
       <c r="Q18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R18" t="n">
-        <v>717</v>
+        <v>315</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2120,17 +2112,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1845960167</t>
+          <t>1156304078</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845960167</t>
+          <t>https://m.place.naver.com/place/1156304078</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2142,25 +2134,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>슈링네일</t>
+          <t>네일스프링</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1355-4556</t>
+          <t>0507-1465-2797</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86 주안역지하상가 198호슈링네일</t>
+          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail___spring</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2170,7 +2162,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2191,17 +2183,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="R19" t="n">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2210,17 +2202,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1276113416</t>
+          <t>2098983836</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1276113416</t>
+          <t>https://m.place.naver.com/place/2098983836</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2232,34 +2224,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>dritn-nail_a_o@naver.com</t>
-        </is>
-      </c>
+          <t>무색</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1325-1015</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 장천로 57 1층</t>
+          <t>인천광역시 미추홀구 주안중로50번길 27-25 2층 204호 무색네일</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://m.themosttimes.co.kr/39655</t>
+          <t>https://www.instagram.com/_musaek</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2289,13 +2273,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>204</v>
+        <v>6</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2304,17 +2288,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1166150967</t>
+          <t>1875342279</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166150967</t>
+          <t>https://m.place.naver.com/place/1875342279</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2326,29 +2310,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아르떼네일</t>
+          <t>두아네일</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>arte__nail_@naver.com</t>
+          <t>zolongky@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1323-0926</t>
+          <t>0507-1367-8198</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
+          <t>인천광역시 미추홀구 능해길 12 용현대우아파트 상가동 201호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/arte__nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2358,12 +2342,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2374,22 +2358,22 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>391</v>
+        <v>69</v>
       </c>
       <c r="Q21" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>450</v>
+        <v>70</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2398,17 +2382,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1775601804</t>
+          <t>1806218865</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1775601804</t>
+          <t>https://m.place.naver.com/place/1806218865</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2420,29 +2404,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>백설공주네일</t>
+          <t>미쓰리손톱</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>k3249093@naver.com</t>
+          <t>minsu900711@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1422-5107</t>
+          <t>0507-1365-1215</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 18</t>
+          <t>인천광역시 동구 솔빛로 21 3층 305호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snow_white.nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2452,7 +2436,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2473,17 +2457,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2492,17 +2476,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1579326733</t>
+          <t>1684702540</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579326733</t>
+          <t>https://m.place.naver.com/place/1684702540</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2514,34 +2498,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>디두네일 D.do nail studio</t>
+          <t>마벨네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ddonail12@naver.com</t>
+          <t>yelee6080@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0507-1423-8033</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
+          <t>인천광역시 동구 수문통로 43 2층 202호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Ukxhxmn</t>
+          <t>https://www.instagram.com/ma._.belle_nail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2562,7 +2542,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2571,13 +2551,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2586,17 +2566,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2003325308</t>
+          <t>1535782131</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003325308</t>
+          <t>https://m.place.naver.com/place/1535782131</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2608,39 +2588,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>인블리네일</t>
+          <t>바비네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bbobbolee2@naver.com</t>
+          <t>zasd43@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>070-7643-2243</t>
+          <t>0507-1351-2629</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
+          <t>인천광역시 중구 개항로 44-1 1층 바비네일</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xhUIxmC</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2656,22 +2636,22 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>416</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1221</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1637</v>
+        <v>5</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2680,17 +2660,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>63265483</t>
+          <t>1166111581</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/63265483</t>
+          <t>https://m.place.naver.com/place/1166111581</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2702,29 +2682,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>아비엥또네일</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>cc3214@naver.com</t>
-        </is>
-      </c>
+          <t>피부&amp;네일 미나뷰티샵</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1340-6448</t>
+          <t>0507-1407-9030</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로351번길 13 1층</t>
+          <t>인천광역시 서구 가정로 246 2층 미나뷰티샵</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_HHusxj</t>
+          <t>https://youtu.be/z9XWwEdP1oM</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2750,7 +2726,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2759,13 +2735,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>428</v>
+        <v>232</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="R25" t="n">
-        <v>430</v>
+        <v>293</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2774,17 +2750,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1754281841</t>
+          <t>1837576332</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754281841</t>
+          <t>https://m.place.naver.com/place/1837576332</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2796,30 +2772,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>송림동네일</t>
+          <t>인블리네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mhsong0103kk@naver.com</t>
+          <t>bbobbolee2@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>070-7643-2243</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 123 104호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/song_rim_dong_nail</t>
+          <t>https://pf.kakao.com/_xhUIxmC</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2840,7 +2820,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2849,13 +2829,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>416</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1221</v>
       </c>
       <c r="R26" t="n">
-        <v>7</v>
+        <v>1637</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2864,17 +2844,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1132799210</t>
+          <t>63265483</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1132799210</t>
+          <t>https://m.place.naver.com/place/63265483</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2886,35 +2866,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>봉숭아네일</t>
+          <t>네일루아</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>yeji4438@naver.com</t>
+          <t>wldud0735@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1439-8987</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송미로 17-4 송림패션몰e동105호 스텔라헤어메이크. 내</t>
+          <t>인천광역시 미추홀구 숙골로87번길 14 107호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_yxmDPxj</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2930,22 +2914,22 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2954,17 +2938,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1910022457</t>
+          <t>1678699503</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910022457</t>
+          <t>https://m.place.naver.com/place/1678699503</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2976,25 +2960,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>미다움네일</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>룩앳미네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>smw3151@naver.com</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0507-1442-0506</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
+          <t>인천광역시 동구 솔빛로 94</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://instagram.com/me_daoom</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3004,7 +2988,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3025,17 +3009,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3044,17 +3028,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1835371224</t>
+          <t>722059236</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835371224</t>
+          <t>https://m.place.naver.com/place/722059236</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3123,13 +3107,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q29" t="n">
         <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3148,7 +3132,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3160,34 +3144,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>유리네일</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>sfsf0525@naver.com</t>
-        </is>
-      </c>
+          <t>네일 날씨 : 맑음.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1353-8292</t>
+          <t>0507-1338-9518</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 38 1층 101호</t>
+          <t>인천광역시 중구 우현로 67 신포지하도상가 37호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uri_nail_</t>
+          <t>http://pf.kakao.com/_xhpxedn</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3208,7 +3188,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3217,13 +3197,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R30" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3232,17 +3212,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1234163292</t>
+          <t>1170688757</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234163292</t>
+          <t>https://m.place.naver.com/place/1170688757</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3254,34 +3234,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일체인지</t>
+          <t>로이네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>j2lang@naver.com</t>
+          <t>wlgus1647@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1350-8716</t>
+          <t>0507-1350-5396</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 상가 B1층 1032호</t>
+          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.change</t>
+          <t>http://pf.kakao.com/_vxkKMs/chat</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3302,7 +3282,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3311,13 +3291,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>313</v>
+        <v>172</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="R31" t="n">
-        <v>315</v>
+        <v>189</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3326,17 +3306,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1330641272</t>
+          <t>1765283529</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330641272</t>
+          <t>https://m.place.naver.com/place/1765283529</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3348,34 +3328,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>반하리뷰티</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>moonvely147@naver.com</t>
-        </is>
-      </c>
+          <t>이루아네일</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1312-2207</t>
+          <t>0507-1400-0973</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 91 3층 반하리뷰티</t>
+          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/banhari0311</t>
+          <t>https://zero.gongbiz.kr/shop/S000070812</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3405,13 +3381,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="Q32" t="n">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="R32" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3420,17 +3396,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1478084350</t>
+          <t>2089020201</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478084350</t>
+          <t>https://m.place.naver.com/place/2089020201</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3442,29 +3418,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>미미네일</t>
+          <t>아르떼네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kensgirl1206@naver.com</t>
+          <t>arte__nail_@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1378-8871</t>
+          <t>0507-1323-0926</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 85 2층 미미네일</t>
+          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/mimi.nail_beauty</t>
+          <t>https://blog.naver.com/arte__nail_</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3479,7 +3455,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3490,7 +3466,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3499,13 +3475,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>55</v>
+        <v>391</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="R33" t="n">
-        <v>70</v>
+        <v>450</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3514,17 +3490,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1738480958</t>
+          <t>1775601804</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1738480958</t>
+          <t>https://m.place.naver.com/place/1775601804</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3536,30 +3512,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>이루아네일</t>
+          <t>네일아이</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1400-0973</t>
+          <t>0507-1324-8849</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
+          <t>인천광역시 중구 개항로 19-1 1층 네일아이</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000070812</t>
+          <t>https://www.instagram.com/_naileye__judi?igsh=NnJic3Y2bnl0enVj&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3589,13 +3565,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="Q34" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3604,17 +3580,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2089020201</t>
+          <t>1827399146</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089020201</t>
+          <t>https://m.place.naver.com/place/1827399146</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3626,29 +3602,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>제로네일</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>seeat_f@naver.com</t>
-        </is>
-      </c>
+          <t>수네일아트</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0507-1359-4583</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
+          <t>인천광역시 미추홀구 주안로90번길 6 4층402호 수네일아트</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zeronail_art</t>
+          <t>http://instagram.com/leh4377</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3683,13 +3651,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>334</v>
+        <v>59</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R35" t="n">
-        <v>339</v>
+        <v>66</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3698,17 +3666,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1613054835</t>
+          <t>1690186584</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1613054835</t>
+          <t>https://m.place.naver.com/place/1690186584</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3720,29 +3688,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1124네일&amp;래쉬</t>
+          <t>오드리뷰티</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>yeps0406@naver.com</t>
+          <t>saerom66@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1363-6780</t>
+          <t>0507-1367-2646</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 동구 인중로680번길 9 1124네일&amp;래쉬</t>
+          <t>인천광역시 미추홀구 주안로 102 오드리뷰티 3층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1124_nail_lash</t>
+          <t>https://www.instagram.com/audreybeauty._1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3768,7 +3736,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3777,13 +3745,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>216</v>
+        <v>13</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="R36" t="n">
-        <v>232</v>
+        <v>76</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3792,17 +3760,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1126025095</t>
+          <t>1722511887</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1126025095</t>
+          <t>https://m.place.naver.com/place/1722511887</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3814,25 +3782,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>수네일아트</t>
+          <t>문제성 손,발 오감네일 도화점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>very_cake@naver.com</t>
+          <t>ogam_foot_nail@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1388-5117</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로90번길 6 4층402호 수네일아트</t>
+          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://instagram.com/leh4377</t>
+          <t>https://blog.naver.com/ogam_foot_nail</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3847,7 +3819,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3867,13 +3839,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>59</v>
+        <v>665</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="R37" t="n">
-        <v>66</v>
+        <v>734</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3882,17 +3854,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1690186584</t>
+          <t>1716147754</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1690186584</t>
+          <t>https://m.place.naver.com/place/1716147754</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3904,29 +3876,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>언니쓰네일샵</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>qgd2557@naver.com</t>
-        </is>
-      </c>
+          <t>백설공주네일</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1333-2250</t>
+          <t>0507-1422-5107</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 옻우물로8번길 10 1층 103호 언니쓰네일샵</t>
+          <t>인천광역시 동구 송현로 18</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uniss_nail</t>
+          <t>https://www.instagram.com/snow_white.nail</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3961,13 +3929,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="R38" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3976,17 +3944,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1983714719</t>
+          <t>1579326733</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1983714719</t>
+          <t>https://m.place.naver.com/place/1579326733</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3998,25 +3966,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일맑음</t>
+          <t>오오샵 가좌점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1489-0530</t>
+          <t>0507-1409-2216</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuneungyeong4</t>
+          <t>https://www.instagram.com/55_allinone_shop</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4051,13 +4019,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>234</v>
+        <v>406</v>
       </c>
       <c r="Q39" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="R39" t="n">
-        <v>303</v>
+        <v>446</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4066,17 +4034,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1539397163</t>
+          <t>1153356301</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539397163</t>
+          <t>https://m.place.naver.com/place/1153356301</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4088,25 +4056,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>룩앳미네일</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>lmy1042@naver.com</t>
-        </is>
-      </c>
+          <t>구이일이샵</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1343-9212</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 94</t>
+          <t>인천광역시 서구 면개포로 15 1층 1호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/9212_nail</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4116,7 +4084,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4137,17 +4105,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4156,17 +4124,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>722059236</t>
+          <t>1957115704</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/722059236</t>
+          <t>https://m.place.naver.com/place/1957115704</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4178,34 +4146,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일루아</t>
+          <t>디에즈네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>wldud0735@naver.com</t>
+          <t>5494778@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1439-8987</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 14 107호</t>
+          <t>인천광역시 미추홀구 염전로202번길 52 104호 디에즈네일</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxmDPxj</t>
+          <t>http://instagram.com/dieznail</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4226,7 +4190,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4235,13 +4199,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="R41" t="n">
-        <v>209</v>
+        <v>251</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4250,17 +4214,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1678699503</t>
+          <t>1520395186</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1678699503</t>
+          <t>https://m.place.naver.com/place/1520395186</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4272,21 +4236,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>고운손</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>미다움네일</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>luna_pic@naver.com</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1442-0506</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
+          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
+          <t>http://instagram.com/me_daoom</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4321,13 +4293,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>166</v>
+        <v>22</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="R42" t="n">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4336,17 +4308,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1926481487</t>
+          <t>1835371224</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926481487</t>
+          <t>https://m.place.naver.com/place/1835371224</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4358,34 +4330,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>봉구네일</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>94rnrdudal@naver.com</t>
-        </is>
-      </c>
+          <t>뷰티송</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1320-0380</t>
+          <t>0507-1399-1155</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86</t>
+          <t>인천광역시 동구 송림로 25 인송상가 106호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bonggu_nail</t>
+          <t>http://pf.kakao.com/_xnIYDxj</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4406,7 +4374,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4415,13 +4383,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="Q43" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4430,17 +4398,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1965492062</t>
+          <t>1018868110</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965492062</t>
+          <t>https://m.place.naver.com/place/1018868110</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4452,29 +4420,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>린다뷰티</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>linda2017v@naver.com</t>
-        </is>
-      </c>
+          <t>네일바이슈</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0507-1422-6954</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로35번길 21-3 1층</t>
+          <t>인천광역시 중구 우현로35번길 21-2 네일바이슈</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lindabeauty.2017/</t>
+          <t>https://www.instagram.com/nailby_sue</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4509,13 +4469,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q44" t="n">
-        <v>246</v>
+        <v>38</v>
       </c>
       <c r="R44" t="n">
-        <v>325</v>
+        <v>116</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4524,17 +4484,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1636516132</t>
+          <t>1304540142</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636516132</t>
+          <t>https://m.place.naver.com/place/1304540142</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4546,25 +4506,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>젤리네일</t>
+          <t>라움뷰티 인천점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mi2013@naver.com</t>
+          <t>raumnail89@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1322-1397</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
+          <t>인천광역시 미추홀구 석정로 360 상가 1층 104호 라움</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1SGa70g</t>
+          <t>https://www.instagram.com/___raum_nail</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4599,13 +4563,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>391</v>
+        <v>242</v>
       </c>
       <c r="Q45" t="n">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="R45" t="n">
-        <v>498</v>
+        <v>286</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4614,17 +4578,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1140244485</t>
+          <t>1287439678</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140244485</t>
+          <t>https://m.place.naver.com/place/1287439678</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4636,24 +4600,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>퍼플</t>
+          <t>네일미래쉬</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>art-lavender@naver.com</t>
+          <t>eungee77@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>070-8692-3990</t>
+          <t>0507-1389-2281</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 21</t>
+          <t>인천광역시 미추홀구 능해길 61-3 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4693,13 +4657,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4708,17 +4672,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1182840289</t>
+          <t>2002602411</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1182840289</t>
+          <t>https://m.place.naver.com/place/2002602411</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4730,25 +4694,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>미추홀구 레벨업 네일뷰티 도화점</t>
+          <t>네일체인지</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1440-6558</t>
+          <t>0507-1350-8716</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 135 해피타운 103호</t>
+          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 상가 B1층 1032호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/levelup_nailstudio</t>
+          <t>https://www.instagram.com/nail.change</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4783,13 +4747,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>855</v>
+        <v>313</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>858</v>
+        <v>315</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4798,17 +4762,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1204613930</t>
+          <t>1330641272</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1204613930</t>
+          <t>https://m.place.naver.com/place/1330641272</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4820,25 +4784,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>마벨네일</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>yelee6080@naver.com</t>
-        </is>
-      </c>
+          <t>주엘로</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1431-9930</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 동구 수문통로 43 2층 202호</t>
+          <t>인천광역시 미추홀구 숙골로112번길 2 2층 203호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ma._.belle_nail</t>
+          <t>https://www.instagram.com/nail_jooello</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4873,13 +4837,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3</v>
+        <v>229</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="R48" t="n">
-        <v>4</v>
+        <v>249</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4888,17 +4852,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1535782131</t>
+          <t>1125345899</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1535782131</t>
+          <t>https://m.place.naver.com/place/1125345899</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4910,34 +4874,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>잉큼잉큼네일</t>
+          <t>네일쿠잉</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>joli96@naver.com</t>
+          <t>sungyoojin12@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>032-772-2929</t>
+          <t>0507-1336-1524</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자유공원로 26-1 잉큼잉큼네일</t>
+          <t>인천광역시 미추홀구 경인로 45 드림타워1층 102호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://www.facebook.com/nail2929</t>
+          <t>https://open.kakao.com/o/sdElcCWf</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4947,7 +4911,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4958,7 +4922,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4967,13 +4931,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="Q49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4982,17 +4946,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>37855121</t>
+          <t>1755114386</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37855121</t>
+          <t>https://m.place.naver.com/place/1755114386</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5004,25 +4968,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>라보떼 뷰티</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>네일오숑</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>dong_fcpae@naver.com</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1377-9030</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
+          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/labeaute7027__</t>
+          <t>https://www.instagram.com/nail_osyong/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5057,13 +5021,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="Q50" t="n">
-        <v>249</v>
+        <v>19</v>
       </c>
       <c r="R50" t="n">
-        <v>516</v>
+        <v>279</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5072,17 +5036,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1828605681</t>
+          <t>1518702391</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828605681</t>
+          <t>https://m.place.naver.com/place/1518702391</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5094,34 +5058,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일,포슬</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>r__r_b@naver.com</t>
-        </is>
-      </c>
+          <t>디두네일 D.do nail studio</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1386-5035</t>
+          <t>0507-1423-8033</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
+          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_poseul_</t>
+          <t>http://pf.kakao.com/_Ukxhxmn</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5142,7 +5102,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5151,13 +5111,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="Q51" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="R51" t="n">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5166,17 +5126,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1050625355</t>
+          <t>2003325308</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050625355</t>
+          <t>https://m.place.naver.com/place/2003325308</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5188,29 +5148,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>주엘로</t>
+          <t>네일혜 도화점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jew_ell@naver.com</t>
+          <t>nailhye_@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1431-9930</t>
+          <t>0507-1487-9095</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로112번길 2 2층 203호</t>
+          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_jooello</t>
+          <t>https://www.instagram.com/_nail.hye/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5245,13 +5205,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="Q52" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R52" t="n">
-        <v>249</v>
+        <v>343</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5260,17 +5220,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1125345899</t>
+          <t>1396481559</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125345899</t>
+          <t>https://m.place.naver.com/place/1396481559</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5282,25 +5242,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>도화네일</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>용쥬르샵 인천본점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>iiidydwn@naver.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1373-9131</t>
+          <t>032-423-2963</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
+          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dohwa_nail_</t>
+          <t>https://blog.naver.com/iiidydwn</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5315,7 +5279,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5335,13 +5299,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>693</v>
+        <v>664</v>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="R53" t="n">
-        <v>695</v>
+        <v>719</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5350,17 +5314,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1155887763</t>
+          <t>1845960167</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155887763</t>
+          <t>https://m.place.naver.com/place/1845960167</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5372,29 +5336,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일 그리고, 봄</t>
+          <t>송림동네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sj330035@naver.com</t>
+          <t>mhsong0103kk@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1354-3366</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로34번길 5 네일 그리고, 봄 2층</t>
+          <t>인천광역시 동구 샛골로 123 104호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_hxlLNb</t>
+          <t>https://www.instagram.com/song_rim_dong_nail</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5409,7 +5369,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5420,7 +5380,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5429,13 +5389,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>114</v>
+        <v>7</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5444,17 +5404,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1402084410</t>
+          <t>1132799210</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1402084410</t>
+          <t>https://m.place.naver.com/place/1132799210</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5466,29 +5426,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일미래쉬</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>eungee77@naver.com</t>
-        </is>
-      </c>
+          <t>네일맑음</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1389-2281</t>
+          <t>0507-1489-0530</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 능해길 61-3 1층</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/yuneungyeong4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5498,7 +5454,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5519,17 +5475,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>62</v>
+        <v>234</v>
       </c>
       <c r="Q55" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="R55" t="n">
-        <v>65</v>
+        <v>303</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5538,17 +5494,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2002602411</t>
+          <t>1539397163</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002602411</t>
+          <t>https://m.place.naver.com/place/1539397163</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5560,29 +5516,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일샤르망</t>
+          <t>the네일샵</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>cea1222@naver.com</t>
+          <t>raphaell1004@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1383-5061</t>
+          <t>0507-1341-2360</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로16번길 7 1층 그레이스타워 네일샤르망</t>
+          <t>인천광역시 동구 화도진로 84 1층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sW2y3z2g</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5592,7 +5548,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5608,22 +5564,22 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5632,17 +5588,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1222205064</t>
+          <t>1183303268</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222205064</t>
+          <t>https://m.place.naver.com/place/1183303268</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5654,29 +5610,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>넬덕</t>
+          <t>라예샵</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>brushlounge@naver.com</t>
+          <t>mh124510@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1469-2126</t>
+          <t>0507-1329-0164</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 405 더로프트2 1층</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 16 1층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nelduck_87?igsh=NHRzanQ1Njd0c2Zy</t>
+          <t>https://blog.naver.com/mh124510</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5691,7 +5647,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5711,13 +5667,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R57" t="n">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5726,17 +5682,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2013586255</t>
+          <t>1698965767</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013586255</t>
+          <t>https://m.place.naver.com/place/1698965767</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5748,34 +5704,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>에스네일</t>
+          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>snail4324@naver.com</t>
+          <t>dritn-nail_a_o@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1406-3132</t>
+          <t>0507-1325-1015</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
+          <t>인천광역시 미추홀구 장천로 57 1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snail0070</t>
+          <t>https://m.themosttimes.co.kr/39655</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5805,13 +5761,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="Q58" t="n">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="R58" t="n">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5820,17 +5776,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>38286683</t>
+          <t>1166150967</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38286683</t>
+          <t>https://m.place.naver.com/place/1166150967</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5842,29 +5798,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>미쓰리손톱</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>minsu900711@naver.com</t>
-        </is>
-      </c>
+          <t>도화네일</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1365-1215</t>
+          <t>0507-1373-9131</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 21 3층 305호</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/dohwa_nail_</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5874,7 +5826,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5895,17 +5847,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>1</v>
+        <v>697</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5914,17 +5866,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1684702540</t>
+          <t>1155887763</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1684702540</t>
+          <t>https://m.place.naver.com/place/1155887763</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5936,29 +5888,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일 연출</t>
+          <t>반디인하우스 도화앨리웨이점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>052young@naver.com</t>
+          <t>bandinhouse_dohwa@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1390-8318</t>
+          <t>0507-1392-8241</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로162번길 22-2 1층</t>
+          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/directing.n</t>
+          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5993,13 +5945,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>14</v>
+        <v>341</v>
       </c>
       <c r="Q60" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="R60" t="n">
-        <v>16</v>
+        <v>420</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6008,17 +5960,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1751393842</t>
+          <t>1485881474</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1751393842</t>
+          <t>https://m.place.naver.com/place/1485881474</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6030,34 +5982,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일혜 도화점</t>
+          <t>네일 그리고, 봄</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>nailhye_@naver.com</t>
+          <t>sj330035@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1487-9095</t>
+          <t>0507-1354-3366</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
+          <t>인천광역시 동구 화도진로34번길 5 네일 그리고, 봄 2층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.hye/</t>
+          <t>http://pf.kakao.com/_hxlLNb</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6078,7 +6030,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6087,13 +6039,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>325</v>
+        <v>104</v>
       </c>
       <c r="Q61" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="R61" t="n">
-        <v>342</v>
+        <v>114</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6102,17 +6054,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1396481559</t>
+          <t>1402084410</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1396481559</t>
+          <t>https://m.place.naver.com/place/1402084410</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6124,29 +6076,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>루미랑네일</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>jine_blog@naver.com</t>
-        </is>
-      </c>
+          <t>잉큼잉큼네일</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1371-1706</t>
+          <t>032-772-2929</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
+          <t>인천광역시 중구 자유공원로 26-1 잉큼잉큼네일</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rumirang_nail</t>
+          <t>http://www.facebook.com/nail2929</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6161,7 +6109,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6181,13 +6129,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>259</v>
+        <v>11</v>
       </c>
       <c r="Q62" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="R62" t="n">
-        <v>313</v>
+        <v>19</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6196,17 +6144,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1156304078</t>
+          <t>37855121</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156304078</t>
+          <t>https://m.place.naver.com/place/37855121</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6218,34 +6166,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일팔레트</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>gkdisgmlwo@naver.com</t>
-        </is>
-      </c>
+          <t>아비엥또네일</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1334-0294</t>
+          <t>0507-1340-6448</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
+          <t>인천광역시 미추홀구 석정로351번길 13 1층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palette_nailll</t>
+          <t>https://pf.kakao.com/_HHusxj</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6266,7 +6210,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6275,13 +6219,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>305</v>
+        <v>429</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>311</v>
+        <v>431</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6290,17 +6234,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1167629339</t>
+          <t>1754281841</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167629339</t>
+          <t>https://m.place.naver.com/place/1754281841</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6312,30 +6256,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>로이네일</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>네일 연출</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>052young@naver.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1350-5396</t>
+          <t>0507-1390-8318</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
+          <t>인천광역시 동구 샛골로162번길 22-2 1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vxkKMs/chat</t>
+          <t>https://www.instagram.com/directing.n</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6356,7 +6304,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6365,13 +6313,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="Q64" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>189</v>
+        <v>16</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6380,17 +6328,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1765283529</t>
+          <t>1751393842</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765283529</t>
+          <t>https://m.place.naver.com/place/1751393842</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6402,29 +6350,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>뾰로롱네일</t>
+          <t>뷰티더한_네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>redberry5@naver.com</t>
+          <t>fom05@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1302-6657</t>
+          <t>0507-1328-7134</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
+          <t>인천광역시 서구 건지로 264 1층 108호 일부</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_adorable_heyrin?igsh=c3dqcThsM3Uzb3Uz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6434,7 +6382,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6455,17 +6403,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R65" t="n">
-        <v>83</v>
+        <v>239</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6474,17 +6422,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2058778627</t>
+          <t>1338980593</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058778627</t>
+          <t>https://m.place.naver.com/place/1338980593</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6496,25 +6444,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>리마인드뷰티</t>
+          <t>봉숭아네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0507-1312-5095</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 109 2층 온다s뷰티</t>
+          <t>인천광역시 동구 송미로 17-4 송림패션몰e동105호 스텔라헤어메이크. 내</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re_mind_beauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6524,7 +6468,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6545,17 +6489,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6564,17 +6508,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1978227491</t>
+          <t>1910022457</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1978227491</t>
+          <t>https://m.place.naver.com/place/1910022457</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6586,34 +6530,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>라움뷰티 인천점</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>raumnail89@naver.com</t>
-        </is>
-      </c>
+          <t>네일샤르망</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1322-1397</t>
+          <t>0507-1383-5061</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 360 상가 1층 104호 라움</t>
+          <t>인천광역시 미추홀구 주안중로16번길 7 1층 그레이스타워 네일샤르망</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/___raum_nail</t>
+          <t>https://open.kakao.com/o/sW2y3z2g</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6643,13 +6583,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>242</v>
+        <v>120</v>
       </c>
       <c r="Q67" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="R67" t="n">
-        <v>286</v>
+        <v>125</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6658,17 +6598,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1287439678</t>
+          <t>1222205064</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1287439678</t>
+          <t>https://m.place.naver.com/place/1222205064</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6680,25 +6620,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>디에즈네일</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>judatv@naver.com</t>
-        </is>
-      </c>
+          <t>미미네일</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1378-8871</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 52 104호 디에즈네일</t>
+          <t>인천광역시 중구 우현로 85 2층 미미네일</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://instagram.com/dieznail</t>
+          <t>http://www.instagram.com/mimi.nail_beauty</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6733,13 +6673,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>225</v>
+        <v>55</v>
       </c>
       <c r="Q68" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R68" t="n">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6748,17 +6688,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1520395186</t>
+          <t>1738480958</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520395186</t>
+          <t>https://m.place.naver.com/place/1738480958</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6770,25 +6710,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>루미네일 Lumi nail</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>아젤리아네일</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>dlwlgus0914@naver.com</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1425-3210</t>
+          <t>0507-1491-3901</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 숭의역 4번출구 힐스테이트 상가 1층 메가커피 뒤쪽</t>
+          <t>인천광역시 서구 장고개로287번길 6-2 1층 101호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sBFtqrHh</t>
+          <t>https://blog.naver.com/dlwlgus0914</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6803,7 +6747,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6814,7 +6758,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6823,13 +6767,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>291</v>
+        <v>132</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R69" t="n">
-        <v>293</v>
+        <v>145</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6838,17 +6782,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>71612272</t>
+          <t>1393226062</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/71612272</t>
+          <t>https://m.place.naver.com/place/1393226062</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6860,25 +6804,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일바이슈</t>
+          <t>넬덕</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>7571khs@naver.com</t>
+          <t>brushlounge@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1469-2126</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로35번길 21-2 네일바이슈</t>
+          <t>인천광역시 미추홀구 석정로 405 더로프트2 1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailby_sue</t>
+          <t>https://www.instagram.com/nelduck_87?igsh=NHRzanQ1Njd0c2Zy</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6913,13 +6861,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="Q70" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6928,17 +6876,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1304540142</t>
+          <t>2013586255</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1304540142</t>
+          <t>https://m.place.naver.com/place/2013586255</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6950,25 +6898,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>바비네일</t>
+          <t>리마인드뷰티</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1351-2629</t>
+          <t>0507-1312-5095</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 중구 개항로 44-1 1층 바비네일</t>
+          <t>인천광역시 동구 송림로 109 2층 온다s뷰티</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/re_mind_beauty</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6978,7 +6926,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6999,17 +6947,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="Q71" t="n">
         <v>2</v>
       </c>
       <c r="R71" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7018,17 +6966,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1166111581</t>
+          <t>1978227491</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166111581</t>
+          <t>https://m.place.naver.com/place/1978227491</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7040,25 +6988,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>무색</t>
+          <t>라보떼 뷰티</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>415eunhasu@naver.com</t>
+          <t>dlatmfrl5824@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1377-9030</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로50번길 27-25 2층 204호 무색네일</t>
+          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_musaek</t>
+          <t>https://www.instagram.com/labeaute7027__</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7093,13 +7045,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2</v>
+        <v>267</v>
       </c>
       <c r="Q72" t="n">
-        <v>4</v>
+        <v>252</v>
       </c>
       <c r="R72" t="n">
-        <v>6</v>
+        <v>519</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7108,17 +7060,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1875342279</t>
+          <t>1828605681</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875342279</t>
+          <t>https://m.place.naver.com/place/1828605681</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7130,29 +7082,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>아젤리아네일</t>
+          <t>네일팔레트</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>dlwlgus0914@naver.com</t>
+          <t>nail4season@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1491-3901</t>
+          <t>0507-1334-0294</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 서구 장고개로287번길 6-2 1층 101호</t>
+          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlwlgus0914</t>
+          <t>https://www.instagram.com/palette_nailll</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7167,7 +7119,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7187,13 +7139,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>131</v>
+        <v>305</v>
       </c>
       <c r="Q73" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R73" t="n">
-        <v>144</v>
+        <v>311</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7202,17 +7154,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1393226062</t>
+          <t>1167629339</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1393226062</t>
+          <t>https://m.place.naver.com/place/1167629339</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7224,34 +7176,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>문제성 손,발 오감네일 도화점</t>
+          <t>젤리네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ogam_foot_nail@naver.com</t>
+          <t>mi2013@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0507-1388-5117</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ogam_foot_nail</t>
+          <t>https://open.kakao.com/o/s1SGa70g</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7261,7 +7209,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7272,7 +7220,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7281,13 +7229,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>664</v>
+        <v>391</v>
       </c>
       <c r="Q74" t="n">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="R74" t="n">
-        <v>733</v>
+        <v>498</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7296,17 +7244,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1716147754</t>
+          <t>1140244485</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716147754</t>
+          <t>https://m.place.naver.com/place/1140244485</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7318,29 +7266,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>오오샵 가좌점</t>
+          <t>유리네일</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>dodofamily_mam@naver.com</t>
+          <t>sfsf0525@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1409-2216</t>
+          <t>0507-1353-8292</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
+          <t>인천광역시 동구 송현로 38 1층 101호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop</t>
+          <t>https://www.instagram.com/uri_nail_</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7375,13 +7323,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>406</v>
+        <v>80</v>
       </c>
       <c r="Q75" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="R75" t="n">
-        <v>446</v>
+        <v>94</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7390,17 +7338,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1153356301</t>
+          <t>1234163292</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153356301</t>
+          <t>https://m.place.naver.com/place/1234163292</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7412,34 +7360,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>마이린 네일</t>
+          <t>린다뷰티</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>myrin_nail@naver.com</t>
+          <t>linda2017v@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1364-9606</t>
+          <t>0507-1422-6954</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
+          <t>인천광역시 중구 우현로35번길 21-3 1층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kqfkxj</t>
+          <t>https://www.instagram.com/lindabeauty.2017/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7460,7 +7408,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7469,13 +7417,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>246</v>
       </c>
       <c r="R76" t="n">
-        <v>207</v>
+        <v>325</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7484,17 +7432,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1373786401</t>
+          <t>1636516132</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1373786401</t>
+          <t>https://m.place.naver.com/place/1636516132</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/동구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/동구_네일샵.xlsx
@@ -1127,7 +1127,11 @@
           <t>네일고운</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>won_jieun@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
@@ -1405,11 +1409,7 @@
           <t>이지네일</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>easynailgainmiga@naver.com</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
         <v>74</v>
       </c>
       <c r="Q12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1774,25 +1774,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>슈링네일</t>
+          <t>네일,포슬</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1355-4556</t>
+          <t>0507-1386-5035</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86 주안역지하상가 198호슈링네일</t>
+          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_poseul_</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1823,17 +1823,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>37</v>
+        <v>408</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="R15" t="n">
-        <v>54</v>
+        <v>449</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1842,12 +1842,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1276113416</t>
+          <t>1050625355</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1276113416</t>
+          <t>https://m.place.naver.com/place/1050625355</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1864,25 +1864,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>네일,포슬</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>뾰로롱네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>redberry5@naver.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1386-5035</t>
+          <t>0507-1302-6657</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
+          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_poseul_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1892,7 +1896,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1913,17 +1917,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="Q16" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>449</v>
+        <v>83</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1932,12 +1936,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1050625355</t>
+          <t>2058778627</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050625355</t>
+          <t>https://m.place.naver.com/place/2058778627</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1954,25 +1958,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>뾰로롱네일</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>루미랑네일</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jine_blog@naver.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1302-6657</t>
+          <t>0507-1371-1706</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/rumirang_nail</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1982,7 +1990,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2003,17 +2011,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="R17" t="n">
-        <v>83</v>
+        <v>315</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2022,12 +2030,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2058778627</t>
+          <t>1156304078</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058778627</t>
+          <t>https://m.place.naver.com/place/1156304078</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2044,25 +2052,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>루미랑네일</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>네일스프링</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>wldus318@naver.com</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1371-1706</t>
+          <t>0507-1465-2797</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
+          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rumirang_nail</t>
+          <t>https://www.instagram.com/nail___spring</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2097,13 +2109,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>261</v>
+        <v>126</v>
       </c>
       <c r="Q18" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>315</v>
+        <v>136</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2112,12 +2124,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1156304078</t>
+          <t>2098983836</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156304078</t>
+          <t>https://m.place.naver.com/place/2098983836</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2134,25 +2146,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>네일스프링</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>무색</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>415eunhasu@naver.com</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1465-2797</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
+          <t>인천광역시 미추홀구 주안중로50번길 27-25 2층 204호 무색네일</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___spring</t>
+          <t>https://www.instagram.com/_musaek</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2187,13 +2199,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2202,12 +2214,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2098983836</t>
+          <t>1875342279</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098983836</t>
+          <t>https://m.place.naver.com/place/1875342279</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2224,21 +2236,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>무색</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>두아네일</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>zolongky@naver.com</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1367-8198</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로50번길 27-25 2층 204호 무색네일</t>
+          <t>인천광역시 미추홀구 능해길 12 용현대우아파트 상가동 201호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_musaek</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2248,7 +2268,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2269,17 +2289,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2288,12 +2308,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1875342279</t>
+          <t>1806218865</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875342279</t>
+          <t>https://m.place.naver.com/place/1806218865</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2310,24 +2330,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>두아네일</t>
+          <t>미쓰리손톱</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>zolongky@naver.com</t>
+          <t>minsu900711@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1367-8198</t>
+          <t>0507-1365-1215</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 능해길 12 용현대우아파트 상가동 201호</t>
+          <t>인천광역시 동구 솔빛로 21 3층 305호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2367,13 +2387,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2382,12 +2402,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1806218865</t>
+          <t>1684702540</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806218865</t>
+          <t>https://m.place.naver.com/place/1684702540</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2404,29 +2424,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>미쓰리손톱</t>
+          <t>마벨네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>minsu900711@naver.com</t>
+          <t>yelee6080@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0507-1365-1215</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 21 3층 305호</t>
+          <t>인천광역시 동구 수문통로 43 2층 202호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ma._.belle_nail</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2436,7 +2452,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2457,17 +2473,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2476,12 +2492,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1684702540</t>
+          <t>1535782131</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1684702540</t>
+          <t>https://m.place.naver.com/place/1535782131</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2498,25 +2514,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>마벨네일</t>
+          <t>바비네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>yelee6080@naver.com</t>
+          <t>zasd43@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1351-2629</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 동구 수문통로 43 2층 202호</t>
+          <t>인천광역시 중구 개항로 44-1 1층 바비네일</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ma._.belle_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2526,7 +2546,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2547,17 +2567,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2566,12 +2586,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1535782131</t>
+          <t>1166111581</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1535782131</t>
+          <t>https://m.place.naver.com/place/1166111581</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2588,29 +2608,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>바비네일</t>
+          <t>피부&amp;네일 미나뷰티샵</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>zasd43@naver.com</t>
+          <t>auflaufl@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1351-2629</t>
+          <t>0507-1407-9030</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 중구 개항로 44-1 1층 바비네일</t>
+          <t>인천광역시 서구 가정로 246 2층 미나뷰티샵</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtu.be/z9XWwEdP1oM</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2620,7 +2640,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2641,17 +2661,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>232</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>293</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2660,12 +2680,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1166111581</t>
+          <t>1837576332</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166111581</t>
+          <t>https://m.place.naver.com/place/1837576332</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2682,25 +2702,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>피부&amp;네일 미나뷰티샵</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>인블리네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>bbobbolee2@naver.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1407-9030</t>
+          <t>070-7643-2243</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 246 2층 미나뷰티샵</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://youtu.be/z9XWwEdP1oM</t>
+          <t>https://pf.kakao.com/_xhUIxmC</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2726,7 +2750,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2735,13 +2759,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>232</v>
+        <v>416</v>
       </c>
       <c r="Q25" t="n">
-        <v>61</v>
+        <v>1221</v>
       </c>
       <c r="R25" t="n">
-        <v>293</v>
+        <v>1637</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2750,12 +2774,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1837576332</t>
+          <t>63265483</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1837576332</t>
+          <t>https://m.place.naver.com/place/63265483</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2772,29 +2796,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>인블리네일</t>
+          <t>네일루아</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bbobbolee2@naver.com</t>
+          <t>wldud0735@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>070-7643-2243</t>
+          <t>0507-1439-8987</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
+          <t>인천광역시 미추홀구 숙골로87번길 14 107호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xhUIxmC</t>
+          <t>http://pf.kakao.com/_yxmDPxj</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2829,13 +2853,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>416</v>
+        <v>206</v>
       </c>
       <c r="Q26" t="n">
-        <v>1221</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1637</v>
+        <v>210</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2844,12 +2868,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>63265483</t>
+          <t>1678699503</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/63265483</t>
+          <t>https://m.place.naver.com/place/1678699503</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2866,39 +2890,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일루아</t>
+          <t>룩앳미네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>wldud0735@naver.com</t>
+          <t>smw3151@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0507-1439-8987</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 14 107호</t>
+          <t>인천광역시 동구 솔빛로 94</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxmDPxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2914,22 +2934,22 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>206</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>210</v>
+        <v>5</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2938,12 +2958,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1678699503</t>
+          <t>722059236</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1678699503</t>
+          <t>https://m.place.naver.com/place/722059236</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2960,25 +2980,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>룩앳미네일</t>
+          <t>올라운더네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>smw3151@naver.com</t>
+          <t>allroundernail@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1359-5371</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 94</t>
+          <t>인천광역시 미추홀구 주안로 116 1층 103 A호 올라운더네일</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/allroundernail</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2988,12 +3012,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3009,17 +3033,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3028,12 +3052,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>722059236</t>
+          <t>1165613309</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/722059236</t>
+          <t>https://m.place.naver.com/place/1165613309</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3050,34 +3074,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>올라운더네일</t>
+          <t>네일 날씨 : 맑음.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>allroundernail@naver.com</t>
+          <t>yolo__ej@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1359-5371</t>
+          <t>0507-1338-9518</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 116 1층 103 A호 올라운더네일</t>
+          <t>인천광역시 중구 우현로 67 신포지하도상가 37호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/allroundernail</t>
+          <t>http://pf.kakao.com/_xhpxedn</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3087,7 +3111,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3098,7 +3122,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3107,13 +3131,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R29" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3122,12 +3146,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1165613309</t>
+          <t>1170688757</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165613309</t>
+          <t>https://m.place.naver.com/place/1170688757</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3144,25 +3168,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>네일 날씨 : 맑음.</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>로이네일</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>wlgus1647@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1338-9518</t>
+          <t>0507-1350-5396</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 67 신포지하도상가 37호</t>
+          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhpxedn</t>
+          <t>http://pf.kakao.com/_vxkKMs/chat</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3197,13 +3225,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="Q30" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R30" t="n">
-        <v>119</v>
+        <v>189</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3212,12 +3240,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1170688757</t>
+          <t>1765283529</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1170688757</t>
+          <t>https://m.place.naver.com/place/1765283529</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3234,29 +3262,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>로이네일</t>
+          <t>이루아네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>wlgus1647@naver.com</t>
+          <t>nec1153@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1350-5396</t>
+          <t>0507-1400-0973</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
+          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vxkKMs/chat</t>
+          <t>https://zero.gongbiz.kr/shop/S000070812</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3282,7 +3310,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3291,13 +3319,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="Q31" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R31" t="n">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3306,12 +3334,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1765283529</t>
+          <t>2089020201</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765283529</t>
+          <t>https://m.place.naver.com/place/2089020201</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3328,30 +3356,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>이루아네일</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>아르떼네일</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>arte__nail_@naver.com</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1400-0973</t>
+          <t>0507-1323-0926</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
+          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000070812</t>
+          <t>https://blog.naver.com/arte__nail_</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3361,7 +3393,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3372,7 +3404,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3381,13 +3413,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>136</v>
+        <v>391</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="R32" t="n">
-        <v>158</v>
+        <v>450</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3396,12 +3428,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2089020201</t>
+          <t>1775601804</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089020201</t>
+          <t>https://m.place.naver.com/place/1775601804</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3418,29 +3450,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>아르떼네일</t>
+          <t>네일아이</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>arte__nail_@naver.com</t>
+          <t>army1300@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1323-0926</t>
+          <t>0507-1324-8849</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
+          <t>인천광역시 중구 개항로 19-1 1층 네일아이</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/arte__nail_</t>
+          <t>https://www.instagram.com/_naileye__judi?igsh=NnJic3Y2bnl0enVj&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3455,7 +3487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3466,7 +3498,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3475,13 +3507,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>391</v>
+        <v>193</v>
       </c>
       <c r="Q33" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>450</v>
+        <v>199</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3490,12 +3522,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1775601804</t>
+          <t>1827399146</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1775601804</t>
+          <t>https://m.place.naver.com/place/1827399146</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3512,25 +3544,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>네일아이</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>수네일아트</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>very_cake@naver.com</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1324-8849</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 중구 개항로 19-1 1층 네일아이</t>
+          <t>인천광역시 미추홀구 주안로90번길 6 4층402호 수네일아트</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_naileye__judi?igsh=NnJic3Y2bnl0enVj&amp;utm_source=qr</t>
+          <t>http://instagram.com/leh4377</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3565,13 +3597,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>193</v>
+        <v>59</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3580,12 +3612,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1827399146</t>
+          <t>1690186584</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1827399146</t>
+          <t>https://m.place.naver.com/place/1690186584</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3602,21 +3634,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>수네일아트</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>오드리뷰티</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>saerom66@naver.com</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1367-2646</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로90번길 6 4층402호 수네일아트</t>
+          <t>인천광역시 미추홀구 주안로 102 오드리뷰티 3층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://instagram.com/leh4377</t>
+          <t>https://www.instagram.com/audreybeauty._1</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3642,7 +3682,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3651,13 +3691,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="R35" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3666,12 +3706,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1690186584</t>
+          <t>1722511887</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1690186584</t>
+          <t>https://m.place.naver.com/place/1722511887</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3688,29 +3728,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>오드리뷰티</t>
+          <t>문제성 손,발 오감네일 도화점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>saerom66@naver.com</t>
+          <t>ogam_foot_nail@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1367-2646</t>
+          <t>0507-1388-5117</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 102 오드리뷰티 3층</t>
+          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreybeauty._1</t>
+          <t>https://blog.naver.com/ogam_foot_nail</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3725,7 +3765,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3736,7 +3776,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3745,13 +3785,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>13</v>
+        <v>665</v>
       </c>
       <c r="Q36" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="R36" t="n">
-        <v>76</v>
+        <v>734</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3760,12 +3800,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1722511887</t>
+          <t>1716147754</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722511887</t>
+          <t>https://m.place.naver.com/place/1716147754</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3782,29 +3822,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>문제성 손,발 오감네일 도화점</t>
+          <t>백설공주네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ogam_foot_nail@naver.com</t>
+          <t>k3249093@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1388-5117</t>
+          <t>0507-1422-5107</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
+          <t>인천광역시 동구 송현로 18</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ogam_foot_nail</t>
+          <t>https://www.instagram.com/snow_white.nail</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3819,7 +3859,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3839,13 +3879,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>665</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="R37" t="n">
-        <v>734</v>
+        <v>52</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3854,12 +3894,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1716147754</t>
+          <t>1579326733</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716147754</t>
+          <t>https://m.place.naver.com/place/1579326733</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3876,25 +3916,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>백설공주네일</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>오오샵 가좌점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dodofamily_mam@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1422-5107</t>
+          <t>0507-1409-2216</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 18</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snow_white.nail</t>
+          <t>https://www.instagram.com/55_allinone_shop</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3929,13 +3973,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>406</v>
       </c>
       <c r="Q38" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="R38" t="n">
-        <v>52</v>
+        <v>446</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3944,12 +3988,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1579326733</t>
+          <t>1153356301</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579326733</t>
+          <t>https://m.place.naver.com/place/1153356301</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -3966,25 +4010,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>오오샵 가좌점</t>
+          <t>구이일이샵</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1409-2216</t>
+          <t>0507-1343-9212</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
+          <t>인천광역시 서구 면개포로 15 1층 1호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop</t>
+          <t>http://instagram.com/9212_nail</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4019,13 +4063,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>406</v>
+        <v>84</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>446</v>
+        <v>85</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4034,12 +4078,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1153356301</t>
+          <t>1957115704</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153356301</t>
+          <t>https://m.place.naver.com/place/1957115704</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4056,25 +4100,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>구이일이샵</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>디에즈네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>tombo613@naver.com</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1343-9212</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 서구 면개포로 15 1층 1호</t>
+          <t>인천광역시 미추홀구 염전로202번길 52 104호 디에즈네일</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://instagram.com/9212_nail</t>
+          <t>http://instagram.com/dieznail</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4109,13 +4153,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>84</v>
+        <v>226</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="R40" t="n">
-        <v>85</v>
+        <v>251</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4124,12 +4168,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1957115704</t>
+          <t>1520395186</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1957115704</t>
+          <t>https://m.place.naver.com/place/1520395186</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4146,25 +4190,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>디에즈네일</t>
+          <t>미다움네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5494778@naver.com</t>
+          <t>luna_pic@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1442-0506</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 52 104호 디에즈네일</t>
+          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://instagram.com/dieznail</t>
+          <t>http://instagram.com/me_daoom</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4199,13 +4247,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>226</v>
+        <v>22</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="R41" t="n">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4214,12 +4262,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1520395186</t>
+          <t>1835371224</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520395186</t>
+          <t>https://m.place.naver.com/place/1835371224</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4236,34 +4284,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>미다움네일</t>
+          <t>뷰티송</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>luna_pic@naver.com</t>
+          <t>beautysong7@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1442-0506</t>
+          <t>0507-1399-1155</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
+          <t>인천광역시 동구 송림로 25 인송상가 106호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://instagram.com/me_daoom</t>
+          <t>http://pf.kakao.com/_xnIYDxj</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4284,7 +4332,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4293,13 +4341,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q42" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4308,12 +4356,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1835371224</t>
+          <t>1018868110</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835371224</t>
+          <t>https://m.place.naver.com/place/1018868110</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4330,30 +4378,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>뷰티송</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>네일바이슈</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7571khs@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0507-1399-1155</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 25 인송상가 106호</t>
+          <t>인천광역시 중구 우현로35번길 21-2 네일바이슈</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnIYDxj</t>
+          <t>https://www.instagram.com/nailby_sue</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4374,7 +4422,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4383,13 +4431,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R43" t="n">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4398,12 +4446,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1018868110</t>
+          <t>1304540142</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1018868110</t>
+          <t>https://m.place.naver.com/place/1304540142</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4420,21 +4468,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일바이슈</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>네일미래쉬</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>eungee77@naver.com</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1389-2281</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로35번길 21-2 네일바이슈</t>
+          <t>인천광역시 미추홀구 능해길 61-3 1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailby_sue</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4444,7 +4500,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4465,17 +4521,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4484,12 +4540,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1304540142</t>
+          <t>2002602411</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1304540142</t>
+          <t>https://m.place.naver.com/place/2002602411</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4600,29 +4656,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일미래쉬</t>
+          <t>주엘로</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>eungee77@naver.com</t>
+          <t>jew_ell@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1389-2281</t>
+          <t>0507-1431-9930</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 능해길 61-3 1층</t>
+          <t>인천광역시 미추홀구 숙골로112번길 2 2층 203호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_jooello</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4632,7 +4688,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4653,17 +4709,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>62</v>
+        <v>229</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="R46" t="n">
-        <v>65</v>
+        <v>249</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4672,12 +4728,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2002602411</t>
+          <t>1125345899</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002602411</t>
+          <t>https://m.place.naver.com/place/1125345899</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4694,25 +4750,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일체인지</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>네일쿠잉</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>sungyoojin12@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1350-8716</t>
+          <t>0507-1336-1524</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 372 아인애비뉴 상가 B1층 1032호</t>
+          <t>인천광역시 미추홀구 경인로 45 드림타워1층 102호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.change</t>
+          <t>https://open.kakao.com/o/sdElcCWf</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4738,7 +4798,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4747,13 +4807,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>313</v>
+        <v>37</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>315</v>
+        <v>37</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4762,12 +4822,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1330641272</t>
+          <t>1755114386</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330641272</t>
+          <t>https://m.place.naver.com/place/1755114386</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4784,25 +4844,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>주엘로</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>이월네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>feb1st-@naver.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1431-9930</t>
+          <t>0507-1403-9322</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로112번길 2 2층 203호</t>
+          <t>인천광역시 미추홀구 미추홀대로733번길 27 제지층 101호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_jooello</t>
+          <t>https://www.instagram.com/ewol.nail/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4828,7 +4892,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4837,13 +4901,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>229</v>
+        <v>8</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>249</v>
+        <v>12</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4852,12 +4916,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1125345899</t>
+          <t>2028521125</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125345899</t>
+          <t>https://m.place.naver.com/place/2028521125</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4874,34 +4938,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일쿠잉</t>
+          <t>네일오숑</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sungyoojin12@naver.com</t>
+          <t>dong_fcpae@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0507-1336-1524</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 45 드림타워1층 102호</t>
+          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sdElcCWf</t>
+          <t>https://www.instagram.com/nail_osyong/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4922,7 +4982,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4931,13 +4991,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R49" t="n">
-        <v>37</v>
+        <v>279</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4946,12 +5006,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1755114386</t>
+          <t>1518702391</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1755114386</t>
+          <t>https://m.place.naver.com/place/1518702391</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4968,30 +5028,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>네일오숑</t>
+          <t>디두네일 D.do nail studio</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>dong_fcpae@naver.com</t>
+          <t>ddonail12@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1423-8033</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
+          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_osyong/</t>
+          <t>http://pf.kakao.com/_Ukxhxmn</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5012,7 +5076,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5021,13 +5085,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>260</v>
+        <v>68</v>
       </c>
       <c r="Q50" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R50" t="n">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5036,12 +5100,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1518702391</t>
+          <t>2003325308</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1518702391</t>
+          <t>https://m.place.naver.com/place/2003325308</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5058,30 +5122,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>디두네일 D.do nail studio</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>네일혜 도화점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>nailhye_@naver.com</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1423-8033</t>
+          <t>0507-1487-9095</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
+          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Ukxhxmn</t>
+          <t>https://www.instagram.com/_nail.hye/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5102,7 +5170,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5111,13 +5179,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>68</v>
+        <v>326</v>
       </c>
       <c r="Q51" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R51" t="n">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5126,12 +5194,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2003325308</t>
+          <t>1396481559</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003325308</t>
+          <t>https://m.place.naver.com/place/1396481559</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5148,29 +5216,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일혜 도화점</t>
+          <t>용쥬르샵 인천본점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nailhye_@naver.com</t>
+          <t>iiidydwn@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1487-9095</t>
+          <t>032-423-2963</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
+          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.hye/</t>
+          <t>https://blog.naver.com/iiidydwn</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5185,7 +5253,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5205,13 +5273,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>326</v>
+        <v>664</v>
       </c>
       <c r="Q52" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="R52" t="n">
-        <v>343</v>
+        <v>719</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5220,12 +5288,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1396481559</t>
+          <t>1845960167</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1396481559</t>
+          <t>https://m.place.naver.com/place/1845960167</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5242,29 +5310,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>용쥬르샵 인천본점</t>
+          <t>송림동네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>iiidydwn@naver.com</t>
+          <t>mhsong0103kk@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>032-423-2963</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
+          <t>인천광역시 동구 샛골로 123 104호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iiidydwn</t>
+          <t>https://www.instagram.com/song_rim_dong_nail</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5279,7 +5343,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5299,13 +5363,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>664</v>
+        <v>7</v>
       </c>
       <c r="Q53" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>719</v>
+        <v>7</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5314,12 +5378,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1845960167</t>
+          <t>1132799210</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845960167</t>
+          <t>https://m.place.naver.com/place/1132799210</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5336,30 +5400,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>송림동네일</t>
+          <t>네일맑음</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mhsong0103kk@naver.com</t>
+          <t>s1514@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1489-0530</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 123 104호</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/song_rim_dong_nail</t>
+          <t>https://www.instagram.com/yuneungyeong4</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5369,7 +5437,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5389,13 +5457,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="R54" t="n">
-        <v>7</v>
+        <v>303</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5404,12 +5472,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1132799210</t>
+          <t>1539397163</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1132799210</t>
+          <t>https://m.place.naver.com/place/1539397163</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5426,25 +5494,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일맑음</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>the네일샵</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>raphaell1004@naver.com</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1489-0530</t>
+          <t>0507-1341-2360</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
+          <t>인천광역시 동구 화도진로 84 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuneungyeong4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5454,7 +5526,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5475,17 +5547,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5494,12 +5566,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1539397163</t>
+          <t>1183303268</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539397163</t>
+          <t>https://m.place.naver.com/place/1183303268</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5516,29 +5588,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>the네일샵</t>
+          <t>라예샵</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>raphaell1004@naver.com</t>
+          <t>mh124510@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1341-2360</t>
+          <t>0507-1329-0164</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 84 1층</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 16 1층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mh124510</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5548,12 +5620,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5569,17 +5641,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5588,12 +5660,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1183303268</t>
+          <t>1698965767</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1183303268</t>
+          <t>https://m.place.naver.com/place/1698965767</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5610,34 +5682,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>라예샵</t>
+          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mh124510@naver.com</t>
+          <t>dritn-nail_a_o@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1329-0164</t>
+          <t>0507-1325-1015</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 16 1층</t>
+          <t>인천광역시 미추홀구 장천로 57 1층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mh124510</t>
+          <t>https://m.themosttimes.co.kr/39655</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5647,7 +5719,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5667,13 +5739,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="R57" t="n">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5682,12 +5754,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1698965767</t>
+          <t>1166150967</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1698965767</t>
+          <t>https://m.place.naver.com/place/1166150967</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5704,29 +5776,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
+          <t>네일보송</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>dritn-nail_a_o@naver.com</t>
+          <t>bvaessd12@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1325-1015</t>
+          <t>0507-1358-4132</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 장천로 57 1층</t>
+          <t>인천광역시 미추홀구 주안로 108 경향프라자 9층 907호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://m.themosttimes.co.kr/39655</t>
+          <t>http://pf.kakao.com/_xkNXIG</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5752,7 +5824,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5761,13 +5833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="Q58" t="n">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5776,12 +5848,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1166150967</t>
+          <t>1803093534</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166150967</t>
+          <t>https://m.place.naver.com/place/1803093534</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5801,7 +5873,11 @@
           <t>도화네일</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>gsqnls2u@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
@@ -6079,7 +6155,11 @@
           <t>잉큼잉큼네일</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>moonmatch@naver.com</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
@@ -6169,7 +6249,11 @@
           <t>아비엥또네일</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>cc3214@naver.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
@@ -6447,7 +6531,11 @@
           <t>봉숭아네일</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>yeji4438@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
@@ -6533,7 +6621,11 @@
           <t>네일샤르망</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>cea1222@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
@@ -6553,7 +6645,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6623,7 +6715,11 @@
           <t>미미네일</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>kensgirl1206@naver.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
@@ -6901,7 +6997,11 @@
           <t>리마인드뷰티</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>bacsubac@naver.com</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
@@ -7048,10 +7148,10 @@
         <v>267</v>
       </c>
       <c r="Q72" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="R72" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7199,7 +7299,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">

--- a/naver-place-crawler/results_nail/동구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/동구_네일샵.xlsx
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1124네일&amp;래쉬</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>yeps0406@naver.com</t>
-        </is>
-      </c>
+          <t>네일아이</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1363-6780</t>
+          <t>0507-1324-8849</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 동구 인중로680번길 9 1124네일&amp;래쉬</t>
+          <t>인천광역시 중구 개항로 19-1 1층 네일아이</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/1124_nail_lash</t>
+          <t>https://www.instagram.com/_naileye__judi?igsh=NnJic3Y2bnl0enVj&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1126025095</t>
+          <t>1827399146</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1126025095</t>
+          <t>https://m.place.naver.com/place/1827399146</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,29 +654,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>퍼플</t>
+          <t>린다뷰티</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>art-lavender@naver.com</t>
+          <t>linda2017v@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>070-8692-3990</t>
+          <t>0507-1422-6954</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 21</t>
+          <t>인천광역시 중구 우현로35번길 21-3 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lindabeauty.2017/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +686,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +707,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>326</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1182840289</t>
+          <t>1636516132</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1182840289</t>
+          <t>https://m.place.naver.com/place/1636516132</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,39 +748,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마이린 네일</t>
+          <t>미쓰리손톱</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>myrin_nail@naver.com</t>
+          <t>minsu900711@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1364-9606</t>
+          <t>0507-1365-1215</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
+          <t>인천광역시 동구 솔빛로 21 3층 305호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_kqfkxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -800,22 +796,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>207</v>
+        <v>1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1373786401</t>
+          <t>1684702540</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1373786401</t>
+          <t>https://m.place.naver.com/place/1684702540</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -846,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>제로네일</t>
+          <t>아르떼네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>seeat_f@naver.com</t>
+          <t>arte__nail_@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1359-4583</t>
+          <t>0507-1323-0926</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
+          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/zeronail_art</t>
+          <t>https://blog.naver.com/arte__nail_</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +879,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,7 +890,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>335</v>
+        <v>391</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="R5" t="n">
-        <v>340</v>
+        <v>450</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1613054835</t>
+          <t>1775601804</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1613054835</t>
+          <t>https://m.place.naver.com/place/1775601804</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -940,34 +936,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>봉구네일</t>
+          <t>네일보송</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>94rnrdudal@naver.com</t>
+          <t>bvaessd12@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1320-0380</t>
+          <t>0507-1358-4132</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86 지하상가 148/173호</t>
+          <t>인천광역시 미추홀구 주안로 108 경향프라자 9층 907호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bonggu_nail</t>
+          <t>http://pf.kakao.com/_xkNXIG</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -988,7 +984,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="Q6" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1965492062</t>
+          <t>1803093534</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965492062</t>
+          <t>https://m.place.naver.com/place/1803093534</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1034,25 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>고운손</t>
+          <t>네일고운</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ghghrjftm@naver.com</t>
+          <t>promemoria11@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1301-1928</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
+          <t>인천광역시 미추홀구 주안로 86 주안역 지하도 상가 109호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
+          <t>https://www.instagram.com/nail_goeun</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>169</v>
+        <v>43</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1926481487</t>
+          <t>1691519525</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926481487</t>
+          <t>https://m.place.naver.com/place/1691519525</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1124,34 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일고운</t>
+          <t>아비엥또네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>won_jieun@naver.com</t>
+          <t>cc3214@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1301-1928</t>
+          <t>0507-1340-6448</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 86 주안역 지하도 상가 109호</t>
+          <t>인천광역시 미추홀구 석정로351번길 13 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_goeun</t>
+          <t>https://pf.kakao.com/_HHusxj</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1172,7 +1172,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>39</v>
+        <v>430</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>432</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1691519525</t>
+          <t>1754281841</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1691519525</t>
+          <t>https://m.place.naver.com/place/1754281841</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>미추홀구 레벨업 네일뷰티 도화점</t>
+          <t>에스네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>anh917759@naver.com</t>
+          <t>snail4324@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1440-6558</t>
+          <t>0507-1406-3132</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 135 해피타운 103호</t>
+          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/levelup_nailstudio</t>
+          <t>https://www.instagram.com/snail0070</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>860</v>
+        <v>74</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="R9" t="n">
-        <v>863</v>
+        <v>147</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1204613930</t>
+          <t>38286683</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1204613930</t>
+          <t>https://m.place.naver.com/place/38286683</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1312,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>왕비네일</t>
+          <t>넬덕</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sulai@naver.com</t>
+          <t>brushlounge@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1443-1136</t>
+          <t>0507-1469-2126</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 수봉안길13번길 2 1층</t>
+          <t>인천광역시 미추홀구 석정로 405 더로프트2 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/queennail1117</t>
+          <t>https://www.instagram.com/nelduck_87?igsh=NHRzanQ1Njd0c2Zy</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2055499585</t>
+          <t>2013586255</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055499585</t>
+          <t>https://m.place.naver.com/place/2013586255</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1406,25 +1406,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>이지네일</t>
+          <t>룩앳미네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1481-8813</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 서구 열우물로282번길 25 103호</t>
+          <t>인천광역시 동구 솔빛로 94</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/easy.nlash</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1434,7 +1430,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1455,17 +1451,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2055850137</t>
+          <t>722059236</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055850137</t>
+          <t>https://m.place.naver.com/place/722059236</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1496,25 +1492,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>에스네일</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>문제성 손,발 오감네일 도화점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ogam_foot_nail@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1406-3132</t>
+          <t>0507-1388-5117</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로43번길 14-1 1층 에스네일</t>
+          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snail0070</t>
+          <t>https://blog.naver.com/ogam_foot_nail</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>74</v>
+        <v>664</v>
       </c>
       <c r="Q12" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="R12" t="n">
-        <v>147</v>
+        <v>733</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>38286683</t>
+          <t>1716147754</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38286683</t>
+          <t>https://m.place.naver.com/place/1716147754</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1586,34 +1586,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>루즈뷰티</t>
+          <t>네일 그리고, 봄</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dbtl0705@naver.com</t>
+          <t>sj330035@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1430-6778</t>
+          <t>0507-1354-3366</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 75 102호</t>
+          <t>인천광역시 동구 화도진로34번길 5 네일 그리고, 봄 2층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/meixiang65956777?igsh=ZWlpbml2dXhieGRu</t>
+          <t>http://pf.kakao.com/_hxlLNb</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1634,7 +1634,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R13" t="n">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,17 +1658,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2040581322</t>
+          <t>1402084410</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040581322</t>
+          <t>https://m.place.naver.com/place/1402084410</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1680,29 +1680,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>루미네일 Lumi nail</t>
+          <t>봉구네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>peanutshome02@naver.com</t>
+          <t>94rnrdudal@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1425-3210</t>
+          <t>0507-1320-0380</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 숭의역 4번출구 힐스테이트 상가 1층 메가커피 뒤쪽</t>
+          <t>인천광역시 미추홀구 주안로 86 지하상가 148/173호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sBFtqrHh</t>
+          <t>https://www.instagram.com/bonggu_nail</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1728,7 +1728,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>292</v>
+        <v>103</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="R14" t="n">
-        <v>294</v>
+        <v>133</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1752,17 +1752,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>71612272</t>
+          <t>1965492062</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/71612272</t>
+          <t>https://m.place.naver.com/place/1965492062</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1774,30 +1774,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일,포슬</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>로이네일</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>charming9827@naver.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1386-5035</t>
+          <t>0507-1350-5396</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
+          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_poseul_</t>
+          <t>http://pf.kakao.com/_vxkKMs/chat</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1818,7 +1822,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1827,13 +1831,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>408</v>
+        <v>172</v>
       </c>
       <c r="Q15" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="R15" t="n">
-        <v>449</v>
+        <v>189</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1842,17 +1846,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1050625355</t>
+          <t>1765283529</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050625355</t>
+          <t>https://m.place.naver.com/place/1765283529</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1864,29 +1868,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>뾰로롱네일</t>
+          <t>루미네일 Lumi nail</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>redberry5@naver.com</t>
+          <t>peanutshome02@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1302-6657</t>
+          <t>0507-1425-3210</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
+          <t>인천광역시 미추홀구 인주대로 5 숭의역 4번출구 힐스테이트 상가 1층 메가커피 뒤쪽</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sBFtqrHh</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1896,7 +1900,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1912,22 +1916,22 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1936,17 +1940,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2058778627</t>
+          <t>71612272</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058778627</t>
+          <t>https://m.place.naver.com/place/71612272</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1958,29 +1962,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>루미랑네일</t>
+          <t>바비네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jine_blog@naver.com</t>
+          <t>zasd43@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1371-1706</t>
+          <t>0507-1351-2629</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
+          <t>인천광역시 중구 개항로 44-1 1층 바비네일</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rumirang_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1990,7 +1994,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2011,17 +2015,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>261</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>315</v>
+        <v>5</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2030,17 +2034,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1156304078</t>
+          <t>1166111581</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156304078</t>
+          <t>https://m.place.naver.com/place/1166111581</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2052,29 +2056,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일스프링</t>
+          <t>아젤리아네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>wldus318@naver.com</t>
+          <t>dlwlgus0914@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1465-2797</t>
+          <t>0507-1491-3901</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
+          <t>인천광역시 서구 장고개로287번길 6-2 1층 101호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail___spring</t>
+          <t>https://blog.naver.com/dlwlgus0914</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2089,7 +2093,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2109,13 +2113,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R18" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2124,17 +2128,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2098983836</t>
+          <t>1393226062</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2098983836</t>
+          <t>https://m.place.naver.com/place/1393226062</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2146,25 +2150,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>무색</t>
+          <t>백설공주네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>415eunhasu@naver.com</t>
+          <t>k3249093@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1422-5107</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로50번길 27-25 2층 204호 무색네일</t>
+          <t>인천광역시 동구 송현로 18</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_musaek</t>
+          <t>https://www.instagram.com/snow_white.nail</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2199,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2214,17 +2222,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1875342279</t>
+          <t>1579326733</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875342279</t>
+          <t>https://m.place.naver.com/place/1579326733</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2236,39 +2244,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>두아네일</t>
+          <t>이루아네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>zolongky@naver.com</t>
+          <t>nec1153@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1367-8198</t>
+          <t>0507-1400-0973</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 능해길 12 용현대우아파트 상가동 201호</t>
+          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://zero.gongbiz.kr/shop/S000070812</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2289,17 +2297,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>69</v>
+        <v>136</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="R20" t="n">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2308,17 +2316,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1806218865</t>
+          <t>2089020201</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806218865</t>
+          <t>https://m.place.naver.com/place/2089020201</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2330,29 +2338,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>미쓰리손톱</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>minsu900711@naver.com</t>
-        </is>
-      </c>
+          <t>루미랑네일</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1365-1215</t>
+          <t>0507-1371-1706</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 21 3층 305호</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 107호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/rumirang_nail</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2362,7 +2366,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2383,17 +2387,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2402,17 +2406,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1684702540</t>
+          <t>1156304078</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1684702540</t>
+          <t>https://m.place.naver.com/place/1156304078</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2424,25 +2428,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>마벨네일</t>
+          <t>제로네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>yelee6080@naver.com</t>
+          <t>seeat_f@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1359-4583</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 동구 수문통로 43 2층 202호</t>
+          <t>인천광역시 미추홀구 석정로302번길 3 1층 102호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ma._.belle_nail</t>
+          <t>https://www.instagram.com/zeronail_art</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2477,13 +2485,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>335</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>340</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2492,17 +2500,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1535782131</t>
+          <t>1613054835</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1535782131</t>
+          <t>https://m.place.naver.com/place/1613054835</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2514,29 +2522,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>바비네일</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>zasd43@naver.com</t>
-        </is>
-      </c>
+          <t>잉큼잉큼네일</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1351-2629</t>
+          <t>032-772-2929</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 중구 개항로 44-1 1층 바비네일</t>
+          <t>인천광역시 중구 자유공원로 26-1 잉큼잉큼네일</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.facebook.com/nail2929</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2546,12 +2550,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2567,17 +2571,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2586,17 +2590,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1166111581</t>
+          <t>37855121</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166111581</t>
+          <t>https://m.place.naver.com/place/37855121</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2608,29 +2612,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>피부&amp;네일 미나뷰티샵</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>auflaufl@naver.com</t>
-        </is>
-      </c>
+          <t>네일더블링</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1407-9030</t>
+          <t>0507-1322-0629</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 246 2층 미나뷰티샵</t>
+          <t>인천광역시 중구 참외전로 141</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://youtu.be/z9XWwEdP1oM</t>
+          <t>http://www.instagram.com/nail_the_bling</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2665,13 +2665,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="Q24" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="R24" t="n">
-        <v>293</v>
+        <v>90</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2680,17 +2680,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1837576332</t>
+          <t>1337603996</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1837576332</t>
+          <t>https://m.place.naver.com/place/1337603996</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2702,34 +2702,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>인블리네일</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>bbobbolee2@naver.com</t>
-        </is>
-      </c>
+          <t>오오샵 가좌점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>070-7643-2243</t>
+          <t>0507-1409-2216</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xhUIxmC</t>
+          <t>https://www.instagram.com/55_allinone_shop</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2750,7 +2746,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2759,13 +2755,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="Q25" t="n">
-        <v>1221</v>
+        <v>40</v>
       </c>
       <c r="R25" t="n">
-        <v>1637</v>
+        <v>446</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2774,17 +2770,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>63265483</t>
+          <t>1153356301</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/63265483</t>
+          <t>https://m.place.naver.com/place/1153356301</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2796,34 +2792,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일루아</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>wldud0735@naver.com</t>
-        </is>
-      </c>
+          <t>구이일이샵</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1439-8987</t>
+          <t>0507-1343-9212</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 14 107호</t>
+          <t>인천광역시 서구 면개포로 15 1층 1호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yxmDPxj</t>
+          <t>http://instagram.com/9212_nail</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2844,7 +2836,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2853,13 +2845,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>206</v>
+        <v>85</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>210</v>
+        <v>86</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2868,17 +2860,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1678699503</t>
+          <t>1957115704</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1678699503</t>
+          <t>https://m.place.naver.com/place/1957115704</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2882,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>룩앳미네일</t>
+          <t>네일바이슈</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>smw3151@naver.com</t>
+          <t>7571khs@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2903,12 +2895,12 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 동구 솔빛로 94</t>
+          <t>인천광역시 중구 우현로35번길 21-2 네일바이슈</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailby_sue</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2918,7 +2910,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2939,17 +2931,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2958,17 +2950,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>722059236</t>
+          <t>1304540142</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/722059236</t>
+          <t>https://m.place.naver.com/place/1304540142</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2980,29 +2972,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>올라운더네일</t>
+          <t>이지네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>allroundernail@naver.com</t>
+          <t>easynailgainmiga@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1359-5371</t>
+          <t>0507-1481-8813</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 116 1층 103 A호 올라운더네일</t>
+          <t>인천광역시 서구 열우물로282번길 25 103호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/allroundernail</t>
+          <t>https://www.instagram.com/easy.nlash</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3017,7 +3009,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3037,13 +3029,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3052,17 +3044,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1165613309</t>
+          <t>2055850137</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1165613309</t>
+          <t>https://m.place.naver.com/place/2055850137</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3074,34 +3066,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일 날씨 : 맑음.</t>
+          <t>라예샵</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>yolo__ej@naver.com</t>
+          <t>mh124510@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1338-9518</t>
+          <t>0507-1329-0164</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 67 신포지하도상가 37호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 16 1층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhpxedn</t>
+          <t>https://blog.naver.com/mh124510</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3111,7 +3103,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3122,7 +3114,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3131,13 +3123,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R29" t="n">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3146,17 +3138,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1170688757</t>
+          <t>1698965767</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1170688757</t>
+          <t>https://m.place.naver.com/place/1698965767</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3168,34 +3160,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>로이네일</t>
+          <t>주엘로</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>wlgus1647@naver.com</t>
+          <t>jew_ell@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1350-5396</t>
+          <t>0507-1431-9930</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 경향프라자 6층</t>
+          <t>인천광역시 미추홀구 숙골로112번길 2 2층 203호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vxkKMs/chat</t>
+          <t>https://www.instagram.com/nail_jooello</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3216,7 +3208,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3225,13 +3217,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="Q30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R30" t="n">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3240,17 +3232,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1765283529</t>
+          <t>1125345899</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765283529</t>
+          <t>https://m.place.naver.com/place/1125345899</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3262,34 +3254,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>이루아네일</t>
+          <t>디에즈네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>nec1153@naver.com</t>
+          <t>tombo613@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0507-1400-0973</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로151번길 4 102동 1층 102호</t>
+          <t>인천광역시 미추홀구 염전로202번길 52 104호 디에즈네일</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000070812</t>
+          <t>http://instagram.com/dieznail</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3319,13 +3307,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R31" t="n">
-        <v>158</v>
+        <v>251</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3334,17 +3322,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2089020201</t>
+          <t>1520395186</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089020201</t>
+          <t>https://m.place.naver.com/place/1520395186</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3356,29 +3344,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아르떼네일</t>
+          <t>오드리뷰티</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>arte__nail_@naver.com</t>
+          <t>saerom66@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1323-0926</t>
+          <t>0507-1367-2646</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로697번길 22 1층 103호</t>
+          <t>인천광역시 미추홀구 주안로 102 오드리뷰티 3층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/arte__nail_</t>
+          <t>https://www.instagram.com/audreybeauty._1</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3393,7 +3381,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3413,13 +3401,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>391</v>
+        <v>13</v>
       </c>
       <c r="Q32" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R32" t="n">
-        <v>450</v>
+        <v>76</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3428,17 +3416,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1775601804</t>
+          <t>1722511887</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1775601804</t>
+          <t>https://m.place.naver.com/place/1722511887</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3450,29 +3438,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일아이</t>
+          <t>퍼플</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>army1300@naver.com</t>
+          <t>art-lavender@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1324-8849</t>
+          <t>070-8692-3990</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 중구 개항로 19-1 1층 네일아이</t>
+          <t>인천광역시 동구 솔빛로 21</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_naileye__judi?igsh=NnJic3Y2bnl0enVj&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3482,7 +3470,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3503,17 +3491,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>193</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>199</v>
+        <v>2</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3522,17 +3510,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1827399146</t>
+          <t>1182840289</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1827399146</t>
+          <t>https://m.place.naver.com/place/1182840289</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3544,25 +3532,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>수네일아트</t>
+          <t>미미네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>very_cake@naver.com</t>
+          <t>kensgirl1206@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1378-8871</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로90번길 6 4층402호 수네일아트</t>
+          <t>인천광역시 중구 우현로 85 2층 미미네일</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://instagram.com/leh4377</t>
+          <t>http://www.instagram.com/mimi.nail_beauty</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3597,13 +3589,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R34" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3612,17 +3604,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1690186584</t>
+          <t>1738480958</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1690186584</t>
+          <t>https://m.place.naver.com/place/1738480958</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3634,29 +3626,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>오드리뷰티</t>
+          <t>네일,포슬</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>saerom66@naver.com</t>
+          <t>yonimiao@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1367-2646</t>
+          <t>0507-1386-5035</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 102 오드리뷰티 3층</t>
+          <t>인천광역시 미추홀구 미추홀대로734번길 25-15 신명프라자 504호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/audreybeauty._1</t>
+          <t>https://www.instagram.com/nail_poseul_</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3682,7 +3674,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3691,13 +3683,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>13</v>
+        <v>408</v>
       </c>
       <c r="Q35" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="R35" t="n">
-        <v>76</v>
+        <v>449</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3706,17 +3698,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1722511887</t>
+          <t>1050625355</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722511887</t>
+          <t>https://m.place.naver.com/place/1050625355</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3728,29 +3720,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>문제성 손,발 오감네일 도화점</t>
+          <t>루즈뷰티</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ogam_foot_nail@naver.com</t>
+          <t>dbtl0705@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1388-5117</t>
+          <t>0507-1430-6778</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 48-25 1층 103호 문제성 손,발 오감네일</t>
+          <t>인천광역시 미추홀구 주안로 75 102호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ogam_foot_nail</t>
+          <t>https://www.instagram.com/meixiang65956777?igsh=ZWlpbml2dXhieGRu</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3765,7 +3757,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3785,13 +3777,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>665</v>
+        <v>48</v>
       </c>
       <c r="Q36" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>734</v>
+        <v>49</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3800,17 +3792,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1716147754</t>
+          <t>2040581322</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1716147754</t>
+          <t>https://m.place.naver.com/place/2040581322</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3822,29 +3814,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>백설공주네일</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>k3249093@naver.com</t>
-        </is>
-      </c>
+          <t>젤리네일</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0507-1422-5107</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 18</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/snow_white.nail</t>
+          <t>https://open.kakao.com/o/s1SGa70g</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3870,7 +3854,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3879,13 +3863,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>392</v>
       </c>
       <c r="Q37" t="n">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="R37" t="n">
-        <v>52</v>
+        <v>499</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3894,17 +3878,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1579326733</t>
+          <t>1140244485</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579326733</t>
+          <t>https://m.place.naver.com/place/1140244485</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3916,29 +3900,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>오오샵 가좌점</t>
+          <t>네일샤르망</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dodofamily_mam@naver.com</t>
+          <t>cea1222@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1409-2216</t>
+          <t>0507-1383-5061</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 1층 108호</t>
+          <t>인천광역시 미추홀구 주안중로16번길 7 1층 그레이스타워 네일샤르망</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/55_allinone_shop</t>
+          <t>https://open.kakao.com/o/sW2y3z2g</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3964,7 +3948,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3973,13 +3957,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>406</v>
+        <v>120</v>
       </c>
       <c r="Q38" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>446</v>
+        <v>125</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3988,17 +3972,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1153356301</t>
+          <t>1222205064</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153356301</t>
+          <t>https://m.place.naver.com/place/1222205064</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4010,25 +3994,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>구이일이샵</t>
+          <t>뾰로롱네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1343-9212</t>
+          <t>0507-1302-6657</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 서구 면개포로 15 1층 1호</t>
+          <t>인천광역시 미추홀구 석바위로53번길 15-3 1층 일부</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://instagram.com/9212_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4038,7 +4022,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4059,17 +4043,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4078,17 +4062,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1957115704</t>
+          <t>2058778627</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1957115704</t>
+          <t>https://m.place.naver.com/place/2058778627</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4100,25 +4084,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>디에즈네일</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>tombo613@naver.com</t>
-        </is>
-      </c>
+          <t>두아네일</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1367-8198</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 염전로202번길 52 104호 디에즈네일</t>
+          <t>인천광역시 미추홀구 능해길 12 용현대우아파트 상가동 201호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://instagram.com/dieznail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4128,7 +4112,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4149,17 +4133,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>226</v>
+        <v>69</v>
       </c>
       <c r="Q40" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>251</v>
+        <v>70</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4168,17 +4152,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1520395186</t>
+          <t>1806218865</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520395186</t>
+          <t>https://m.place.naver.com/place/1806218865</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4190,29 +4174,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>미다움네일</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>luna_pic@naver.com</t>
-        </is>
-      </c>
+          <t>네일스프링</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1442-0506</t>
+          <t>0507-1465-2797</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
+          <t>인천광역시 미추홀구 미추로19번길 41 1층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://instagram.com/me_daoom</t>
+          <t>https://www.instagram.com/nail___spring</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4247,13 +4227,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="Q41" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="R41" t="n">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4262,17 +4242,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1835371224</t>
+          <t>2098983836</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835371224</t>
+          <t>https://m.place.naver.com/place/2098983836</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4284,34 +4264,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>뷰티송</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>beautysong7@naver.com</t>
-        </is>
-      </c>
+          <t>미다움네일</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1399-1155</t>
+          <t>0507-1442-0506</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 25 인송상가 106호</t>
+          <t>인천광역시 미추홀구 미추로 20 101호 미다움네일</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnIYDxj</t>
+          <t>http://instagram.com/me_daoom</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4332,7 +4308,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4341,13 +4317,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="R42" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4356,17 +4332,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1018868110</t>
+          <t>1835371224</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1018868110</t>
+          <t>https://m.place.naver.com/place/1835371224</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4378,25 +4354,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일바이슈</t>
+          <t>용쥬르샵 인천본점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>7571khs@naver.com</t>
+          <t>iiidydwn@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>032-423-2963</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로35번길 21-2 네일바이슈</t>
+          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailby_sue</t>
+          <t>https://blog.naver.com/iiidydwn</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4411,7 +4391,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4431,13 +4411,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>78</v>
+        <v>664</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="R43" t="n">
-        <v>116</v>
+        <v>719</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4446,17 +4426,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1304540142</t>
+          <t>1845960167</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1304540142</t>
+          <t>https://m.place.naver.com/place/1845960167</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4468,24 +4448,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일미래쉬</t>
+          <t>the네일샵</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>eungee77@naver.com</t>
+          <t>glue123456@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1389-2281</t>
+          <t>0507-1341-2360</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 능해길 61-3 1층</t>
+          <t>인천광역시 동구 화도진로 84 1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4525,13 +4505,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4540,17 +4520,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2002602411</t>
+          <t>1183303268</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002602411</t>
+          <t>https://m.place.naver.com/place/1183303268</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4562,29 +4542,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>라움뷰티 인천점</t>
+          <t>반디인하우스 도화앨리웨이점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>raumnail89@naver.com</t>
+          <t>bandinhouse_dohwa@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1322-1397</t>
+          <t>0507-1392-8241</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 360 상가 1층 104호 라움</t>
+          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/___raum_nail</t>
+          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4610,7 +4590,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4619,13 +4599,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>242</v>
+        <v>341</v>
       </c>
       <c r="Q45" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="R45" t="n">
-        <v>286</v>
+        <v>420</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4634,17 +4614,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1287439678</t>
+          <t>1485881474</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1287439678</t>
+          <t>https://m.place.naver.com/place/1485881474</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4656,34 +4636,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>주엘로</t>
+          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jew_ell@naver.com</t>
+          <t>dritn-nail_a_o@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1431-9930</t>
+          <t>0507-1325-1015</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로112번길 2 2층 203호</t>
+          <t>인천광역시 미추홀구 장천로 57 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_jooello</t>
+          <t>https://m.themosttimes.co.kr/39655</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4713,13 +4693,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>229</v>
+        <v>87</v>
       </c>
       <c r="Q46" t="n">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="R46" t="n">
-        <v>249</v>
+        <v>204</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4728,17 +4708,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1125345899</t>
+          <t>1166150967</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125345899</t>
+          <t>https://m.place.naver.com/place/1166150967</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4750,29 +4730,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일쿠잉</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>sungyoojin12@naver.com</t>
-        </is>
-      </c>
+          <t>수네일아트</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0507-1336-1524</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 45 드림타워1층 102호</t>
+          <t>인천광역시 미추홀구 주안로90번길 6 4층402호 수네일아트</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sdElcCWf</t>
+          <t>http://instagram.com/leh4377</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4798,7 +4770,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4807,13 +4779,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R47" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4822,17 +4794,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1755114386</t>
+          <t>1690186584</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1755114386</t>
+          <t>https://m.place.naver.com/place/1690186584</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4844,29 +4816,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>이월네일</t>
+          <t>네일오숑</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb1st-@naver.com</t>
+          <t>won_jieun@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0507-1403-9322</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로733번길 27 제지층 101호</t>
+          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ewol.nail/</t>
+          <t>https://www.instagram.com/nail_osyong/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4892,7 +4860,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4901,13 +4869,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>8</v>
+        <v>260</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="R48" t="n">
-        <v>12</v>
+        <v>279</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4916,17 +4884,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2028521125</t>
+          <t>1518702391</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028521125</t>
+          <t>https://m.place.naver.com/place/1518702391</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4938,25 +4906,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일오숑</t>
+          <t>미추홀구 레벨업 네일뷰티 도화점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>dong_fcpae@naver.com</t>
+          <t>anh917759@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1440-6558</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안서로53번길 18 101호</t>
+          <t>인천광역시 미추홀구 경인로 135 해피타운 103호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_osyong/</t>
+          <t>https://www.instagram.com/levelup_nailstudio</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4991,13 +4963,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>260</v>
+        <v>867</v>
       </c>
       <c r="Q49" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>279</v>
+        <v>870</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5006,17 +4978,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1518702391</t>
+          <t>1204613930</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1518702391</t>
+          <t>https://m.place.naver.com/place/1204613930</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5028,29 +5000,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>디두네일 D.do nail studio</t>
+          <t>네일루아</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ddonail12@naver.com</t>
+          <t>wldud0735@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1423-8033</t>
+          <t>0507-1439-8987</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
+          <t>인천광역시 미추홀구 숙골로87번길 14 107호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Ukxhxmn</t>
+          <t>http://pf.kakao.com/_yxmDPxj</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5085,13 +5057,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>68</v>
+        <v>206</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5100,17 +5072,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2003325308</t>
+          <t>1678699503</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003325308</t>
+          <t>https://m.place.naver.com/place/1678699503</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5122,29 +5094,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일혜 도화점</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>nailhye_@naver.com</t>
-        </is>
-      </c>
+          <t>네일팔레트</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1487-9095</t>
+          <t>0507-1334-0294</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
+          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.hye/</t>
+          <t>https://www.instagram.com/palette_nailll</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5179,13 +5147,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="Q51" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="R51" t="n">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5194,17 +5162,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1396481559</t>
+          <t>1167629339</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1396481559</t>
+          <t>https://m.place.naver.com/place/1167629339</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5216,29 +5184,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>용쥬르샵 인천본점</t>
+          <t>봉숭아네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>iiidydwn@naver.com</t>
+          <t>a_nail@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>032-423-2963</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 352 2층 용쥬르샵</t>
+          <t>인천광역시 동구 송미로 17-4 송림패션몰e동105호 스텔라헤어메이크. 내</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iiidydwn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5248,12 +5212,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5269,17 +5233,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>664</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>719</v>
+        <v>0</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5288,17 +5252,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1845960167</t>
+          <t>1910022457</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845960167</t>
+          <t>https://m.place.naver.com/place/1910022457</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5310,25 +5274,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>송림동네일</t>
+          <t>유리네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mhsong0103kk@naver.com</t>
+          <t>sfsf0525@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1353-8292</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 123 104호</t>
+          <t>인천광역시 동구 송현로 38 1층 101호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/song_rim_dong_nail</t>
+          <t>https://www.instagram.com/uri_nail_</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5363,13 +5331,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R53" t="n">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5378,17 +5346,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1132799210</t>
+          <t>1234163292</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1132799210</t>
+          <t>https://m.place.naver.com/place/1234163292</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5400,34 +5368,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일맑음</t>
+          <t>디두네일 D.do nail studio</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>s1514@naver.com</t>
+          <t>ddonail12@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1489-0530</t>
+          <t>0507-1423-8033</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
+          <t>인천광역시 미추홀구 인주대로 5 2층 A-225호 디두네일</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuneungyeong4</t>
+          <t>http://pf.kakao.com/_Ukxhxmn</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5448,7 +5416,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5457,13 +5425,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>234</v>
+        <v>68</v>
       </c>
       <c r="Q54" t="n">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="R54" t="n">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5472,17 +5440,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1539397163</t>
+          <t>2003325308</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539397163</t>
+          <t>https://m.place.naver.com/place/2003325308</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5494,29 +5462,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>the네일샵</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>raphaell1004@naver.com</t>
-        </is>
-      </c>
+          <t>피부&amp;네일 미나뷰티샵</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1341-2360</t>
+          <t>0507-1407-9030</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 84 1층</t>
+          <t>인천광역시 서구 가정로 246 2층 미나뷰티샵</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtu.be/z9XWwEdP1oM</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5526,7 +5490,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5547,17 +5511,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5566,17 +5530,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1183303268</t>
+          <t>1837576332</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1183303268</t>
+          <t>https://m.place.naver.com/place/1837576332</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5588,29 +5552,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>라예샵</t>
+          <t>고운손</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mh124510@naver.com</t>
+          <t>ghghrjftm@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1329-0164</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 16 1층</t>
+          <t>인천광역시 미추홀구 낙섬중로 129 상가6동 212호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mh124510</t>
+          <t>https://www.instagram.com/gowoon_son/profilecard/?igsh=MWJ1cnU5dnFhaG9x</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5625,7 +5585,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5645,13 +5605,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="Q56" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5660,17 +5620,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1698965767</t>
+          <t>1926481487</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1698965767</t>
+          <t>https://m.place.naver.com/place/1926481487</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5682,34 +5642,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>풋앤바디로 페디크루 내성발톱 무좀 발각질 인솔</t>
+          <t>라움뷰티 인천점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>dritn-nail_a_o@naver.com</t>
+          <t>raumnail89@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1325-1015</t>
+          <t>0507-1322-1397</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 장천로 57 1층</t>
+          <t>인천광역시 미추홀구 석정로 360 상가 1층 104호 라움</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://m.themosttimes.co.kr/39655</t>
+          <t>https://www.instagram.com/___raum_nail</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5730,7 +5690,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5739,13 +5699,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>87</v>
+        <v>242</v>
       </c>
       <c r="Q57" t="n">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="R57" t="n">
-        <v>204</v>
+        <v>286</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5754,17 +5714,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1166150967</t>
+          <t>1287439678</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166150967</t>
+          <t>https://m.place.naver.com/place/1287439678</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5776,29 +5736,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>네일보송</t>
+          <t>인블리네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bvaessd12@naver.com</t>
+          <t>bbobbolee2@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1358-4132</t>
+          <t>070-7643-2243</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 108 경향프라자 9층 907호</t>
+          <t>인천광역시 미추홀구 미추홀대로719번길 4 부성파인 2층 인블리네일</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xkNXIG</t>
+          <t>https://pf.kakao.com/_xhUIxmC</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5833,13 +5793,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>73</v>
+        <v>417</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>1221</v>
       </c>
       <c r="R58" t="n">
-        <v>77</v>
+        <v>1638</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5848,17 +5808,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1803093534</t>
+          <t>63265483</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1803093534</t>
+          <t>https://m.place.naver.com/place/63265483</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5870,29 +5830,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>도화네일</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>gsqnls2u@naver.com</t>
-        </is>
-      </c>
+          <t>무색</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0507-1373-9131</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
+          <t>인천광역시 미추홀구 주안중로50번길 27-25 2층 204호 무색네일</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dohwa_nail_</t>
+          <t>https://www.instagram.com/_musaek</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5927,13 +5879,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>695</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R59" t="n">
-        <v>697</v>
+        <v>6</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5942,17 +5894,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1155887763</t>
+          <t>1875342279</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155887763</t>
+          <t>https://m.place.naver.com/place/1875342279</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5964,29 +5916,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>반디인하우스 도화앨리웨이점</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>bandinhouse_dohwa@naver.com</t>
-        </is>
-      </c>
+          <t>기므네일</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1392-8241</t>
+          <t>0507-1419-7245</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 5 인천앨리웨이 라이프동 2층 반디인하우스</t>
+          <t>인천광역시 미추홀구 숙골로87번길 5 2층15호 (더샵 인천스카이타워2단지</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://instagram.com/bandinhouse_dohwa_alleyway</t>
+          <t>https://www.instagram.com/kim_e_nail</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6021,13 +5969,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>341</v>
+        <v>61</v>
       </c>
       <c r="Q60" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>420</v>
+        <v>61</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6036,17 +5984,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1485881474</t>
+          <t>2068109873</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1485881474</t>
+          <t>https://m.place.naver.com/place/2068109873</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6058,34 +6006,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일 그리고, 봄</t>
+          <t>1124네일&amp;래쉬</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sj330035@naver.com</t>
+          <t>yeps0406@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1354-3366</t>
+          <t>0507-1363-6780</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로34번길 5 네일 그리고, 봄 2층</t>
+          <t>인천광역시 동구 인중로680번길 9 1124네일&amp;래쉬</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_hxlLNb</t>
+          <t>https://www.instagram.com/1124_nail_lash</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6106,7 +6054,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6115,13 +6063,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R61" t="n">
-        <v>114</v>
+        <v>232</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6130,17 +6078,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1402084410</t>
+          <t>1126025095</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1402084410</t>
+          <t>https://m.place.naver.com/place/1126025095</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6152,29 +6100,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>잉큼잉큼네일</t>
+          <t>리마인드뷰티</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>moonmatch@naver.com</t>
+          <t>bacsubac@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>032-772-2929</t>
+          <t>0507-1312-5095</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 중구 자유공원로 26-1 잉큼잉큼네일</t>
+          <t>인천광역시 동구 송림로 109 2층 온다s뷰티</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://www.facebook.com/nail2929</t>
+          <t>https://www.instagram.com/re_mind_beauty</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6189,7 +6137,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6209,13 +6157,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6224,17 +6172,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>37855121</t>
+          <t>1978227491</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37855121</t>
+          <t>https://m.place.naver.com/place/1978227491</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6246,34 +6194,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>아비엥또네일</t>
+          <t>이월네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>cc3214@naver.com</t>
+          <t>feb1st-@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1340-6448</t>
+          <t>0507-1403-9322</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로351번길 13 1층</t>
+          <t>인천광역시 미추홀구 미추홀대로733번길 27 제지층 101호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_HHusxj</t>
+          <t>https://www.instagram.com/ewol.nail/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6303,13 +6251,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>429</v>
+        <v>8</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R63" t="n">
-        <v>431</v>
+        <v>12</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6318,17 +6266,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1754281841</t>
+          <t>2028521125</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754281841</t>
+          <t>https://m.place.naver.com/place/2028521125</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6340,34 +6288,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일 연출</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>052young@naver.com</t>
-        </is>
-      </c>
+          <t>뷰티더한_네일</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1390-8318</t>
+          <t>0507-1328-7134</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로162번길 22-2 1층</t>
+          <t>인천광역시 서구 건지로 264 1층 108호 일부</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/directing.n</t>
+          <t>https://www.instagram.com/nail_adorable_heyrin?igsh=c3dqcThsM3Uzb3Uz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6377,7 +6321,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6397,13 +6341,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>14</v>
+        <v>236</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>16</v>
+        <v>240</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6412,17 +6356,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1751393842</t>
+          <t>1338980593</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1751393842</t>
+          <t>https://m.place.naver.com/place/1338980593</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6434,29 +6378,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>뷰티더한_네일</t>
+          <t>올라운더네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>fom05@naver.com</t>
+          <t>allroundernail@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1328-7134</t>
+          <t>0507-1359-5371</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 건지로 264 1층 108호 일부</t>
+          <t>인천광역시 미추홀구 주안로 116 1층 103 A호 올라운더네일</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_adorable_heyrin?igsh=c3dqcThsM3Uzb3Uz</t>
+          <t>https://blog.naver.com/allroundernail</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6471,7 +6415,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6491,13 +6435,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>235</v>
+        <v>71</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>239</v>
+        <v>74</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6506,17 +6450,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1338980593</t>
+          <t>1165613309</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338980593</t>
+          <t>https://m.place.naver.com/place/1165613309</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6528,25 +6472,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>봉숭아네일</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>yeji4438@naver.com</t>
-        </is>
-      </c>
+          <t>네일 연출</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1390-8318</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송미로 17-4 송림패션몰e동105호 스텔라헤어메이크. 내</t>
+          <t>인천광역시 동구 샛골로162번길 22-2 1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/directing.n</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6556,7 +6500,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6577,17 +6521,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6596,17 +6540,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1910022457</t>
+          <t>1751393842</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1910022457</t>
+          <t>https://m.place.naver.com/place/1751393842</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6618,29 +6562,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일샤르망</t>
+          <t>네일혜 도화점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>cea1222@naver.com</t>
+          <t>nailhye_@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1383-5061</t>
+          <t>0507-1487-9095</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안중로16번길 7 1층 그레이스타워 네일샤르망</t>
+          <t>인천광역시 미추홀구 한나루로599번길 21 1층 101호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sW2y3z2g</t>
+          <t>https://www.instagram.com/_nail.hye/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6666,7 +6610,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6675,13 +6619,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>120</v>
+        <v>328</v>
       </c>
       <c r="Q67" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="R67" t="n">
-        <v>125</v>
+        <v>345</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6690,17 +6634,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1222205064</t>
+          <t>1396481559</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222205064</t>
+          <t>https://m.place.naver.com/place/1396481559</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6712,29 +6656,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>미미네일</t>
+          <t>라보떼 뷰티</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>kensgirl1206@naver.com</t>
+          <t>dlatmfrl5824@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1378-8871</t>
+          <t>0507-1377-9030</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 85 2층 미미네일</t>
+          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/mimi.nail_beauty</t>
+          <t>https://www.instagram.com/labeaute7027__</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6769,13 +6713,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>55</v>
+        <v>268</v>
       </c>
       <c r="Q68" t="n">
-        <v>15</v>
+        <v>255</v>
       </c>
       <c r="R68" t="n">
-        <v>70</v>
+        <v>523</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6784,17 +6728,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1738480958</t>
+          <t>1828605681</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1738480958</t>
+          <t>https://m.place.naver.com/place/1828605681</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6806,29 +6750,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>아젤리아네일</t>
+          <t>네일쿠잉</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>dlwlgus0914@naver.com</t>
+          <t>sungyoojin12@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1491-3901</t>
+          <t>0507-1336-1524</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 서구 장고개로287번길 6-2 1층 101호</t>
+          <t>인천광역시 미추홀구 경인로 45 드림타워1층 102호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlwlgus0914</t>
+          <t>https://open.kakao.com/o/sdElcCWf</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6843,7 +6787,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6854,7 +6798,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6863,13 +6807,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="Q69" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6878,17 +6822,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1393226062</t>
+          <t>1755114386</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1393226062</t>
+          <t>https://m.place.naver.com/place/1755114386</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6900,34 +6844,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>넬덕</t>
+          <t>마이린 네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>brushlounge@naver.com</t>
+          <t>myrin_nail@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1469-2126</t>
+          <t>0507-1364-9606</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 405 더로프트2 1층</t>
+          <t>인천광역시 미추홀구 주안로 108 1층 112호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nelduck_87?igsh=NHRzanQ1Njd0c2Zy</t>
+          <t>http://pf.kakao.com/_kqfkxj</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6948,7 +6892,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6957,13 +6901,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="Q70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R70" t="n">
-        <v>35</v>
+        <v>207</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6972,17 +6916,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2013586255</t>
+          <t>1373786401</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2013586255</t>
+          <t>https://m.place.naver.com/place/1373786401</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6994,34 +6938,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>리마인드뷰티</t>
+          <t>뷰티송</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>bacsubac@naver.com</t>
+          <t>beautysong7@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1312-5095</t>
+          <t>0507-1399-1155</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 109 2층 온다s뷰티</t>
+          <t>인천광역시 동구 송림로 25 인송상가 106호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re_mind_beauty</t>
+          <t>http://pf.kakao.com/_xnIYDxj</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7042,7 +6986,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7051,13 +6995,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Q71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7066,17 +7010,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1978227491</t>
+          <t>1018868110</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1978227491</t>
+          <t>https://m.place.naver.com/place/1018868110</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7088,29 +7032,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>라보떼 뷰티</t>
+          <t>네일맑음</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>dlatmfrl5824@naver.com</t>
+          <t>s1514@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1377-9030</t>
+          <t>0507-1489-0530</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 720 2층 라보떼뷰티</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 303호(3층)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/labeaute7027__</t>
+          <t>https://www.instagram.com/yuneungyeong4</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7145,13 +7089,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="Q72" t="n">
-        <v>253</v>
+        <v>69</v>
       </c>
       <c r="R72" t="n">
-        <v>520</v>
+        <v>303</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7160,17 +7104,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1828605681</t>
+          <t>1539397163</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828605681</t>
+          <t>https://m.place.naver.com/place/1539397163</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7182,29 +7126,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>네일팔레트</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>nail4season@naver.com</t>
-        </is>
-      </c>
+          <t>송림동네일</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0507-1334-0294</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 용현동 685-12 제상가3동 203호</t>
+          <t>인천광역시 동구 샛골로 123 104호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palette_nailll</t>
+          <t>https://www.instagram.com/song_rim_dong_nail</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7239,13 +7175,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>305</v>
+        <v>7</v>
       </c>
       <c r="Q73" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>311</v>
+        <v>7</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7254,17 +7190,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1167629339</t>
+          <t>1132799210</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167629339</t>
+          <t>https://m.place.naver.com/place/1132799210</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7276,25 +7212,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>젤리네일</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>mi2013@naver.com</t>
-        </is>
-      </c>
+          <t>도화네일</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1373-9131</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로719번길 29 1층 젤리네일</t>
+          <t>인천광역시 미추홀구 숙골로95번길 33 캠퍼스프라자 2층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s1SGa70g</t>
+          <t>https://www.instagram.com/dohwa_nail_</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7320,7 +7256,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7329,13 +7265,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>391</v>
+        <v>695</v>
       </c>
       <c r="Q74" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>498</v>
+        <v>697</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7344,17 +7280,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1140244485</t>
+          <t>1155887763</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140244485</t>
+          <t>https://m.place.naver.com/place/1155887763</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7366,29 +7302,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>유리네일</t>
+          <t>네일미래쉬</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>sfsf0525@naver.com</t>
+          <t>eungee77@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1353-8292</t>
+          <t>0507-1389-2281</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 38 1층 101호</t>
+          <t>인천광역시 미추홀구 능해길 61-3 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uri_nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7398,7 +7334,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7419,17 +7355,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="Q75" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R75" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7438,17 +7374,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1234163292</t>
+          <t>2002602411</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234163292</t>
+          <t>https://m.place.naver.com/place/2002602411</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7460,29 +7396,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>린다뷰티</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>linda2017v@naver.com</t>
-        </is>
-      </c>
+          <t>마벨네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0507-1422-6954</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로35번길 21-3 1층</t>
+          <t>인천광역시 동구 수문통로 43 2층 202호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lindabeauty.2017/</t>
+          <t>https://www.instagram.com/ma._.belle_nail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7517,13 +7445,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="Q76" t="n">
-        <v>246</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>325</v>
+        <v>4</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7532,17 +7460,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1636516132</t>
+          <t>1535782131</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636516132</t>
+          <t>https://m.place.naver.com/place/1535782131</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
